--- a/NotasGeologiaPublicationList_Updated.xlsx
+++ b/NotasGeologiaPublicationList_Updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\mariantoc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C90BC6A6-A806-40F0-B0E4-5672B45794CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72EA1E4A-8F63-4969-96D0-2C4B2178CBE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4798" uniqueCount="4400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4818" uniqueCount="4425">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -13527,6 +13527,81 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/glaciers.html#SchubertC1970</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The five giganuclear geological and tectonic forces that give rise to the Gulf of Mexico. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crisis y esperanza: La ciencia en Venezuela y los desafíos del presente. </t>
+  </si>
+  <si>
+    <t>MAYA. Revista de Geociencias, Febrero 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benjamín Scharifker </t>
+  </si>
+  <si>
+    <t>Boletín de la Academia de Ciencias Físicas, Matemáticas y Naturales, Volumen LXXXV, Número 2, pp. 33 – 38, 2025</t>
+  </si>
+  <si>
+    <t>Cenozoic landscape evolution of the southern part of the Gran Sabana, Southwestern Venezuela. Implications for the occurrence of gold and diamond placers.</t>
+  </si>
+  <si>
+    <t>Dohrenwend, J. C.; Yanez , G.; Lowry, G.</t>
+  </si>
+  <si>
+    <t>Shield US Geological Survey, Bulletin 212, No. 4, 1995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Macroforaminíferos y edad de la Formación Punta Mosquito (Grupo Carnero) de la Isla de Margarita, Venezuela. </t>
+  </si>
+  <si>
+    <t>J. Butterlin</t>
+  </si>
+  <si>
+    <t>Boletín Informativo de la Asociación Venezolana de Geología, Minería y Petróleo, Volumen 13, Número 10, Octubre 1970</t>
+  </si>
+  <si>
+    <t>Catastro Espeleológico Nacional (Venezuela hasta 1977)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los foraminíferos vivos y sedimentados del margen continental de Venezuela (Resumen). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montserrat Domingo de Miró </t>
+  </si>
+  <si>
+    <t>Acta Geológica Hispana, VI, No. 4, pp. 102 – 108, 1971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petrografía orgánica de la secuencia Cretácica de dos pozos del suroeste de la Cuenca Barinas – Apure. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nidya Jordan </t>
+  </si>
+  <si>
+    <t>Revista Técnica de Intevep, Volumen 4, Número 2, pp. 153 – 161, Julio 1984</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/topics.html#AlvarezE2026</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#SharikerB2025</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/minerals.html#DohrenwendJCetal1995</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#ButterlinJ1970</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/speleology.html#Catastro</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#DomingoM1971</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/geochemistry.html#JordanN1984</t>
   </si>
 </sst>
 </file>
@@ -42619,13 +42694,13 @@
         <v>4274</v>
       </c>
       <c r="G1152" s="1" t="str">
-        <f t="shared" ref="G1152:G1204" si="37">HYPERLINK(F1152)</f>
+        <f t="shared" ref="G1152:G1206" si="37">HYPERLINK(F1152)</f>
         <v>https://mariantoc.github.io/ecology.html#HoyosJ1982</v>
       </c>
     </row>
     <row r="1153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1153">
-        <f t="shared" ref="A1153:A1199" si="38">A1152+1</f>
+        <f t="shared" ref="A1153:A1206" si="38">A1152+1</f>
         <v>1152</v>
       </c>
       <c r="B1153" t="s">
@@ -43637,7 +43712,7 @@
       <c r="E1193" t="s">
         <v>4375</v>
       </c>
-      <c r="F1193" s="8" t="s">
+      <c r="F1193" t="s">
         <v>4393</v>
       </c>
       <c r="G1193" s="1" t="str">
@@ -43662,7 +43737,7 @@
       <c r="E1194" t="s">
         <v>4378</v>
       </c>
-      <c r="F1194" s="8" t="s">
+      <c r="F1194" t="s">
         <v>4394</v>
       </c>
       <c r="G1194" s="1" t="str">
@@ -43687,7 +43762,7 @@
       <c r="E1195" t="s">
         <v>4381</v>
       </c>
-      <c r="F1195" s="8" t="s">
+      <c r="F1195" t="s">
         <v>4395</v>
       </c>
       <c r="G1195" s="1" t="str">
@@ -43712,7 +43787,7 @@
       <c r="E1196" t="s">
         <v>4384</v>
       </c>
-      <c r="F1196" s="8" t="s">
+      <c r="F1196" t="s">
         <v>4396</v>
       </c>
       <c r="G1196" s="1" t="str">
@@ -43737,7 +43812,7 @@
       <c r="E1197" t="s">
         <v>4387</v>
       </c>
-      <c r="F1197" s="8" t="s">
+      <c r="F1197" t="s">
         <v>4397</v>
       </c>
       <c r="G1197" s="1" t="str">
@@ -43762,7 +43837,7 @@
       <c r="E1198" t="s">
         <v>4390</v>
       </c>
-      <c r="F1198" s="8" t="s">
+      <c r="F1198" t="s">
         <v>4398</v>
       </c>
       <c r="G1198" s="1" t="str">
@@ -43787,7 +43862,7 @@
       <c r="E1199" t="s">
         <v>4392</v>
       </c>
-      <c r="F1199" s="8" t="s">
+      <c r="F1199" t="s">
         <v>4399</v>
       </c>
       <c r="G1199" s="1" t="str">
@@ -43796,91 +43871,223 @@
       </c>
     </row>
     <row r="1200" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1200" s="7" t="s">
-        <v>4315</v>
-      </c>
-      <c r="G1200" s="1"/>
-    </row>
-    <row r="1201" spans="6:7" x14ac:dyDescent="0.3">
-      <c r="F1201" s="7" t="s">
-        <v>4315</v>
-      </c>
-      <c r="G1201" s="1"/>
-    </row>
-    <row r="1202" spans="6:7" x14ac:dyDescent="0.3">
-      <c r="F1202" s="7" t="s">
-        <v>4315</v>
-      </c>
-      <c r="G1202" s="1"/>
-    </row>
-    <row r="1203" spans="6:7" x14ac:dyDescent="0.3">
-      <c r="F1203" s="7" t="s">
-        <v>4315</v>
-      </c>
-      <c r="G1203" s="1"/>
-    </row>
-    <row r="1204" spans="6:7" x14ac:dyDescent="0.3">
-      <c r="F1204" s="7" t="s">
-        <v>4315</v>
-      </c>
-      <c r="G1204" s="1"/>
-    </row>
-    <row r="1205" spans="6:7" x14ac:dyDescent="0.3">
-      <c r="F1205" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1206" spans="6:7" x14ac:dyDescent="0.3">
-      <c r="F1206" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1207" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="A1200">
+        <f t="shared" si="38"/>
+        <v>1199</v>
+      </c>
+      <c r="B1200" t="s">
+        <v>4400</v>
+      </c>
+      <c r="C1200" t="s">
+        <v>2703</v>
+      </c>
+      <c r="D1200">
+        <v>2026</v>
+      </c>
+      <c r="E1200" t="s">
+        <v>4402</v>
+      </c>
+      <c r="F1200" s="8" t="s">
+        <v>4418</v>
+      </c>
+      <c r="G1200" s="1" t="str">
+        <f t="shared" si="37"/>
+        <v>https://mariantoc.github.io/topics.html#AlvarezE2026</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1201">
+        <f t="shared" si="38"/>
+        <v>1200</v>
+      </c>
+      <c r="B1201" t="s">
+        <v>4401</v>
+      </c>
+      <c r="C1201" t="s">
+        <v>4403</v>
+      </c>
+      <c r="D1201">
+        <v>2025</v>
+      </c>
+      <c r="E1201" t="s">
+        <v>4404</v>
+      </c>
+      <c r="F1201" s="8" t="s">
+        <v>4419</v>
+      </c>
+      <c r="G1201" s="1" t="str">
+        <f t="shared" si="37"/>
+        <v>https://mariantoc.github.io/biography.html#SharikerB2025</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1202">
+        <f t="shared" si="38"/>
+        <v>1201</v>
+      </c>
+      <c r="B1202" t="s">
+        <v>4405</v>
+      </c>
+      <c r="C1202" t="s">
+        <v>4406</v>
+      </c>
+      <c r="D1202">
+        <v>1995</v>
+      </c>
+      <c r="E1202" t="s">
+        <v>4407</v>
+      </c>
+      <c r="F1202" s="8" t="s">
+        <v>4420</v>
+      </c>
+      <c r="G1202" s="1" t="str">
+        <f t="shared" si="37"/>
+        <v>https://mariantoc.github.io/minerals.html#DohrenwendJCetal1995</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1203">
+        <f t="shared" si="38"/>
+        <v>1202</v>
+      </c>
+      <c r="B1203" t="s">
+        <v>4408</v>
+      </c>
+      <c r="C1203" t="s">
+        <v>4409</v>
+      </c>
+      <c r="D1203">
+        <v>1970</v>
+      </c>
+      <c r="E1203" t="s">
+        <v>4410</v>
+      </c>
+      <c r="F1203" s="8" t="s">
+        <v>4421</v>
+      </c>
+      <c r="G1203" s="1" t="str">
+        <f t="shared" si="37"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#ButterlinJ1970</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1204">
+        <f t="shared" si="38"/>
+        <v>1203</v>
+      </c>
+      <c r="B1204" t="s">
+        <v>4411</v>
+      </c>
+      <c r="D1204">
+        <v>1977</v>
+      </c>
+      <c r="E1204" t="s">
+        <v>4365</v>
+      </c>
+      <c r="F1204" s="8" t="s">
+        <v>4422</v>
+      </c>
+      <c r="G1204" s="1" t="str">
+        <f t="shared" si="37"/>
+        <v>https://mariantoc.github.io/speleology.html#Catastro</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1205">
+        <f t="shared" si="38"/>
+        <v>1204</v>
+      </c>
+      <c r="B1205" t="s">
+        <v>4412</v>
+      </c>
+      <c r="C1205" t="s">
+        <v>4413</v>
+      </c>
+      <c r="D1205">
+        <v>1971</v>
+      </c>
+      <c r="E1205" t="s">
+        <v>4414</v>
+      </c>
+      <c r="F1205" s="8" t="s">
+        <v>4423</v>
+      </c>
+      <c r="G1205" s="1" t="str">
+        <f t="shared" si="37"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#DomingoM1971</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1206">
+        <f t="shared" si="38"/>
+        <v>1205</v>
+      </c>
+      <c r="B1206" t="s">
+        <v>4415</v>
+      </c>
+      <c r="C1206" t="s">
+        <v>4416</v>
+      </c>
+      <c r="D1206">
+        <v>1984</v>
+      </c>
+      <c r="E1206" t="s">
+        <v>4417</v>
+      </c>
+      <c r="F1206" s="8" t="s">
+        <v>4424</v>
+      </c>
+      <c r="G1206" s="1" t="str">
+        <f t="shared" si="37"/>
+        <v>https://mariantoc.github.io/geochemistry.html#JordanN1984</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1207" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1208" spans="6:7" x14ac:dyDescent="0.3">
+    <row r="1208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1208" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1209" spans="6:7" x14ac:dyDescent="0.3">
+    <row r="1209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1209" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1210" spans="6:7" x14ac:dyDescent="0.3">
+    <row r="1210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1210" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1211" spans="6:7" x14ac:dyDescent="0.3">
+    <row r="1211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1211" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1212" spans="6:7" x14ac:dyDescent="0.3">
+    <row r="1212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1212" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1213" spans="6:7" x14ac:dyDescent="0.3">
+    <row r="1213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1213" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1214" spans="6:7" x14ac:dyDescent="0.3">
+    <row r="1214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1214" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1215" spans="6:7" x14ac:dyDescent="0.3">
+    <row r="1215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1215" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1216" spans="6:7" x14ac:dyDescent="0.3">
+    <row r="1216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1216" s="7" t="s">
         <v>4315</v>
       </c>

--- a/NotasGeologiaPublicationList_Updated.xlsx
+++ b/NotasGeologiaPublicationList_Updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\mariantoc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72EA1E4A-8F63-4969-96D0-2C4B2178CBE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6AC06CB-BDAA-4785-84EA-B73F067D3A8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4818" uniqueCount="4425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4839" uniqueCount="4452">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -13602,6 +13602,87 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/geochemistry.html#JordanN1984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neotectónica de la Cuenca de Barlovento, Venezuela. </t>
+  </si>
+  <si>
+    <t>Ollarves, R.; Audemard, F.; Espinola, E.; Hernández, J.; Rojas, E.; Alezones, R.; Falcón, R.</t>
+  </si>
+  <si>
+    <t>Ponencias FUNVISIS, Proyecto GEODINOS (FONACIT), pp. 1 – 12, 2004</t>
+  </si>
+  <si>
+    <t>Los depósitos de mena titanífera de San Quintín Central, Estado Yaracuy. Génesis, carateres geológicos y estimación de reservas.</t>
+  </si>
+  <si>
+    <t>Simón E. Rodríguez y Guillermo Aňez M. Disertación basada en el trabajo de campo de Domingo Rodríguez; G. N. Torrealba; C. Velasco; A. Franco; I. Quintero y J. H. Contreras</t>
+  </si>
+  <si>
+    <t>Boletín de Geología del Ministerio de Energía y Minas, Dirección General de Minas y Geología, Volumen XIII, Número 24, Agosto 1978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuevas y simas en cuarcitas y meta-limolitas del Grupo Roraima, Meseta Guaiquinima, Estado Bolívar. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Szczerban, E.; Urbani, F.; Colveé, P. </t>
+  </si>
+  <si>
+    <t>Boletín de la Sociedad Venezolana de Espeleología, Volumen8, Número 16, Octubre 1977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stratigraphic columns modeling and cyclicity analysis of the Misoa Formation, Maracaibo Lake, Venezuela, using Markov chains. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soto, M. B.; Durán, E. L.; Aldana, M. </t>
+  </si>
+  <si>
+    <t>Geofísica Internacional, Vol. 53, No. 3, pp. 277 – 288, 2014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recursos y reservas de hidrocarburos en Venezuela. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alberto Finol </t>
+  </si>
+  <si>
+    <t>Petrorenova. Revista de la Energía, Volumen 4, Número 31, Marzo 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La importancia de los informes técnicos estandarizados en minería. </t>
+  </si>
+  <si>
+    <t>MAYA. Revista de Geociencias, Marzo 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esperanza y luto en el Antropoceno: Entendiendo el duelo ecológico. </t>
+  </si>
+  <si>
+    <t>Antonio Machado-Allison</t>
+  </si>
+  <si>
+    <t>Boletín de la Academia de Ciencias Físicas, Matemáticas y Naturales, Vol. LXXXV, Número 2, pp. 23 – 31, 2025</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/structural.html#OllarvesRetal2004</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/minerals.html#RodriguezSEetal1978</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/speleology.html#SzcerbanEetal1977</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/geophysics.html#SotoMBetal2014</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/fields.html#FinolA2026</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/minerals.html#CastroM2026</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/ecology.html#MachadoA2025</t>
   </si>
 </sst>
 </file>
@@ -42694,13 +42775,13 @@
         <v>4274</v>
       </c>
       <c r="G1152" s="1" t="str">
-        <f t="shared" ref="G1152:G1206" si="37">HYPERLINK(F1152)</f>
+        <f t="shared" ref="G1152:G1213" si="37">HYPERLINK(F1152)</f>
         <v>https://mariantoc.github.io/ecology.html#HoyosJ1982</v>
       </c>
     </row>
     <row r="1153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1153">
-        <f t="shared" ref="A1153:A1206" si="38">A1152+1</f>
+        <f t="shared" ref="A1153:A1213" si="38">A1152+1</f>
         <v>1152</v>
       </c>
       <c r="B1153" t="s">
@@ -43887,7 +43968,7 @@
       <c r="E1200" t="s">
         <v>4402</v>
       </c>
-      <c r="F1200" s="8" t="s">
+      <c r="F1200" t="s">
         <v>4418</v>
       </c>
       <c r="G1200" s="1" t="str">
@@ -43912,7 +43993,7 @@
       <c r="E1201" t="s">
         <v>4404</v>
       </c>
-      <c r="F1201" s="8" t="s">
+      <c r="F1201" t="s">
         <v>4419</v>
       </c>
       <c r="G1201" s="1" t="str">
@@ -43937,7 +44018,7 @@
       <c r="E1202" t="s">
         <v>4407</v>
       </c>
-      <c r="F1202" s="8" t="s">
+      <c r="F1202" t="s">
         <v>4420</v>
       </c>
       <c r="G1202" s="1" t="str">
@@ -43962,7 +44043,7 @@
       <c r="E1203" t="s">
         <v>4410</v>
       </c>
-      <c r="F1203" s="8" t="s">
+      <c r="F1203" t="s">
         <v>4421</v>
       </c>
       <c r="G1203" s="1" t="str">
@@ -43984,7 +44065,7 @@
       <c r="E1204" t="s">
         <v>4365</v>
       </c>
-      <c r="F1204" s="8" t="s">
+      <c r="F1204" t="s">
         <v>4422</v>
       </c>
       <c r="G1204" s="1" t="str">
@@ -44009,7 +44090,7 @@
       <c r="E1205" t="s">
         <v>4414</v>
       </c>
-      <c r="F1205" s="8" t="s">
+      <c r="F1205" t="s">
         <v>4423</v>
       </c>
       <c r="G1205" s="1" t="str">
@@ -44034,7 +44115,7 @@
       <c r="E1206" t="s">
         <v>4417</v>
       </c>
-      <c r="F1206" s="8" t="s">
+      <c r="F1206" t="s">
         <v>4424</v>
       </c>
       <c r="G1206" s="1" t="str">
@@ -44043,38 +44124,178 @@
       </c>
     </row>
     <row r="1207" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1207" s="7" t="s">
-        <v>4315</v>
+      <c r="A1207">
+        <f t="shared" si="38"/>
+        <v>1206</v>
+      </c>
+      <c r="B1207" t="s">
+        <v>4425</v>
+      </c>
+      <c r="C1207" t="s">
+        <v>4426</v>
+      </c>
+      <c r="D1207">
+        <v>2004</v>
+      </c>
+      <c r="E1207" t="s">
+        <v>4427</v>
+      </c>
+      <c r="F1207" s="8" t="s">
+        <v>4445</v>
+      </c>
+      <c r="G1207" s="1" t="str">
+        <f t="shared" si="37"/>
+        <v>https://mariantoc.github.io/structural.html#OllarvesRetal2004</v>
       </c>
     </row>
     <row r="1208" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1208" s="7" t="s">
-        <v>4315</v>
+      <c r="A1208">
+        <f t="shared" si="38"/>
+        <v>1207</v>
+      </c>
+      <c r="B1208" t="s">
+        <v>4428</v>
+      </c>
+      <c r="C1208" t="s">
+        <v>4429</v>
+      </c>
+      <c r="D1208">
+        <v>1978</v>
+      </c>
+      <c r="E1208" t="s">
+        <v>4430</v>
+      </c>
+      <c r="F1208" s="8" t="s">
+        <v>4446</v>
+      </c>
+      <c r="G1208" s="1" t="str">
+        <f t="shared" si="37"/>
+        <v>https://mariantoc.github.io/minerals.html#RodriguezSEetal1978</v>
       </c>
     </row>
     <row r="1209" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1209" s="7" t="s">
-        <v>4315</v>
+      <c r="A1209">
+        <f t="shared" si="38"/>
+        <v>1208</v>
+      </c>
+      <c r="B1209" t="s">
+        <v>4431</v>
+      </c>
+      <c r="C1209" t="s">
+        <v>4432</v>
+      </c>
+      <c r="D1209">
+        <v>1977</v>
+      </c>
+      <c r="E1209" t="s">
+        <v>4433</v>
+      </c>
+      <c r="F1209" s="8" t="s">
+        <v>4447</v>
+      </c>
+      <c r="G1209" s="1" t="str">
+        <f t="shared" si="37"/>
+        <v>https://mariantoc.github.io/speleology.html#SzcerbanEetal1977</v>
       </c>
     </row>
     <row r="1210" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1210" s="7" t="s">
-        <v>4315</v>
+      <c r="A1210">
+        <f t="shared" si="38"/>
+        <v>1209</v>
+      </c>
+      <c r="B1210" t="s">
+        <v>4434</v>
+      </c>
+      <c r="C1210" t="s">
+        <v>4435</v>
+      </c>
+      <c r="D1210">
+        <v>2014</v>
+      </c>
+      <c r="E1210" t="s">
+        <v>4436</v>
+      </c>
+      <c r="F1210" s="8" t="s">
+        <v>4448</v>
+      </c>
+      <c r="G1210" s="1" t="str">
+        <f t="shared" si="37"/>
+        <v>https://mariantoc.github.io/geophysics.html#SotoMBetal2014</v>
       </c>
     </row>
     <row r="1211" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1211" s="7" t="s">
-        <v>4315</v>
+      <c r="A1211">
+        <f t="shared" si="38"/>
+        <v>1210</v>
+      </c>
+      <c r="B1211" t="s">
+        <v>4437</v>
+      </c>
+      <c r="C1211" t="s">
+        <v>4438</v>
+      </c>
+      <c r="D1211">
+        <v>2026</v>
+      </c>
+      <c r="E1211" t="s">
+        <v>4439</v>
+      </c>
+      <c r="F1211" s="8" t="s">
+        <v>4449</v>
+      </c>
+      <c r="G1211" s="1" t="str">
+        <f t="shared" si="37"/>
+        <v>https://mariantoc.github.io/fields.html#FinolA2026</v>
       </c>
     </row>
     <row r="1212" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1212" s="7" t="s">
-        <v>4315</v>
+      <c r="A1212">
+        <f t="shared" si="38"/>
+        <v>1211</v>
+      </c>
+      <c r="B1212" t="s">
+        <v>4440</v>
+      </c>
+      <c r="C1212" t="s">
+        <v>2880</v>
+      </c>
+      <c r="D1212">
+        <v>2026</v>
+      </c>
+      <c r="E1212" t="s">
+        <v>4441</v>
+      </c>
+      <c r="F1212" s="8" t="s">
+        <v>4450</v>
+      </c>
+      <c r="G1212" s="1" t="str">
+        <f t="shared" si="37"/>
+        <v>https://mariantoc.github.io/minerals.html#CastroM2026</v>
       </c>
     </row>
     <row r="1213" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1213" s="7" t="s">
-        <v>4315</v>
+      <c r="A1213">
+        <f t="shared" si="38"/>
+        <v>1212</v>
+      </c>
+      <c r="B1213" t="s">
+        <v>4442</v>
+      </c>
+      <c r="C1213" t="s">
+        <v>4443</v>
+      </c>
+      <c r="D1213">
+        <v>2025</v>
+      </c>
+      <c r="E1213" t="s">
+        <v>4444</v>
+      </c>
+      <c r="F1213" s="8" t="s">
+        <v>4451</v>
+      </c>
+      <c r="G1213" s="1" t="str">
+        <f t="shared" si="37"/>
+        <v>https://mariantoc.github.io/ecology.html#MachadoA2025</v>
       </c>
     </row>
     <row r="1214" spans="1:7" x14ac:dyDescent="0.3">

--- a/NotasGeologiaPublicationList_Updated.xlsx
+++ b/NotasGeologiaPublicationList_Updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\mariantoc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6AC06CB-BDAA-4785-84EA-B73F067D3A8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4FA6468-5279-453C-A7A1-452AAB831761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4839" uniqueCount="4452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4860" uniqueCount="4477">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -13683,6 +13683,81 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/ecology.html#MachadoA2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lago de Asfalto de Guanoco. La nueva Faja Petrolífera. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jesús Prato </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La isla Groenlandia. Su geografía, geología y sus eventos históricos. </t>
+  </si>
+  <si>
+    <t>Liverpool Petroleum LLC, Febrero 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Co – Mn Mineralizations in the Ni laterite deposits of Loma Caribe (Dominican Republic) and Loma de Hierro (Venezuela). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domenech, C,; Villanova de Benavent, C.; Proenza, J. A.; Tauler, E.; Lara, L.; Galí, S.; Soler, J. M.; Campeny, M.; Ibaňez – Insa, J. </t>
+  </si>
+  <si>
+    <t>MDPI, 12, 927, 2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An Estimate of Recoverable Heavy Oil Resources of the Orinoco Oil Belt, Venezuela. </t>
+  </si>
+  <si>
+    <t>Schenk, C. J.; Cook, T. A.; Charpentier, R. R.; Pollastro, R. M.; Klett, T. R.; Tennyson, M. E.; Kirschbaum, M. A.; Brownfield, M. E.; Pitman, J. K.</t>
+  </si>
+  <si>
+    <t>U S Geological Service, World Petroleum Resources Project, October 2009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My start to oil geological field work in Venezuela in 1945. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peter Bitterli </t>
+  </si>
+  <si>
+    <t>Boletín de Historia de las Geociencias en Venezuela, Número 63, Abril 1998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuevas exploraciones espeleológicas en la Sierra de Pacairima, Guayana Venezolana. </t>
+  </si>
+  <si>
+    <t>Wilmer Pérez La Riva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Middle Eocene foreland sediments covered by Late Oligocene foredeep turbidites on Margarita Island, northeastern Venezuela. </t>
+  </si>
+  <si>
+    <t>Oliver Macsotay and Tulio Peraza</t>
+  </si>
+  <si>
+    <t>Transactions of the 16th Caribbean Geological Conference, Barbados. Caribbean Journal of Earth Science 39, pp. 105 – 111, 2005</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/fields.html#PratoJ2026</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/topics.html#GoddardDA2026</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/minerals.html#DomenechCetal2022</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/fields.html#SchenkCJetal2009</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#BitterliPBaselB1945</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/speleology.html#PerezW1977</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#MacsotayOPerazaT2005</t>
   </si>
 </sst>
 </file>
@@ -42775,13 +42850,13 @@
         <v>4274</v>
       </c>
       <c r="G1152" s="1" t="str">
-        <f t="shared" ref="G1152:G1213" si="37">HYPERLINK(F1152)</f>
+        <f t="shared" ref="G1152:G1215" si="37">HYPERLINK(F1152)</f>
         <v>https://mariantoc.github.io/ecology.html#HoyosJ1982</v>
       </c>
     </row>
     <row r="1153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1153">
-        <f t="shared" ref="A1153:A1213" si="38">A1152+1</f>
+        <f t="shared" ref="A1153:A1216" si="38">A1152+1</f>
         <v>1152</v>
       </c>
       <c r="B1153" t="s">
@@ -44140,7 +44215,7 @@
       <c r="E1207" t="s">
         <v>4427</v>
       </c>
-      <c r="F1207" s="8" t="s">
+      <c r="F1207" t="s">
         <v>4445</v>
       </c>
       <c r="G1207" s="1" t="str">
@@ -44165,7 +44240,7 @@
       <c r="E1208" t="s">
         <v>4430</v>
       </c>
-      <c r="F1208" s="8" t="s">
+      <c r="F1208" t="s">
         <v>4446</v>
       </c>
       <c r="G1208" s="1" t="str">
@@ -44190,7 +44265,7 @@
       <c r="E1209" t="s">
         <v>4433</v>
       </c>
-      <c r="F1209" s="8" t="s">
+      <c r="F1209" t="s">
         <v>4447</v>
       </c>
       <c r="G1209" s="1" t="str">
@@ -44215,7 +44290,7 @@
       <c r="E1210" t="s">
         <v>4436</v>
       </c>
-      <c r="F1210" s="8" t="s">
+      <c r="F1210" t="s">
         <v>4448</v>
       </c>
       <c r="G1210" s="1" t="str">
@@ -44240,7 +44315,7 @@
       <c r="E1211" t="s">
         <v>4439</v>
       </c>
-      <c r="F1211" s="8" t="s">
+      <c r="F1211" t="s">
         <v>4449</v>
       </c>
       <c r="G1211" s="1" t="str">
@@ -44265,7 +44340,7 @@
       <c r="E1212" t="s">
         <v>4441</v>
       </c>
-      <c r="F1212" s="8" t="s">
+      <c r="F1212" t="s">
         <v>4450</v>
       </c>
       <c r="G1212" s="1" t="str">
@@ -44290,7 +44365,7 @@
       <c r="E1213" t="s">
         <v>4444</v>
       </c>
-      <c r="F1213" s="8" t="s">
+      <c r="F1213" t="s">
         <v>4451</v>
       </c>
       <c r="G1213" s="1" t="str">
@@ -44299,86 +44374,226 @@
       </c>
     </row>
     <row r="1214" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1214" s="7" t="s">
-        <v>4315</v>
+      <c r="A1214">
+        <f t="shared" si="38"/>
+        <v>1213</v>
+      </c>
+      <c r="B1214" t="s">
+        <v>4452</v>
+      </c>
+      <c r="C1214" t="s">
+        <v>4453</v>
+      </c>
+      <c r="D1214">
+        <v>2026</v>
+      </c>
+      <c r="E1214" t="s">
+        <v>4439</v>
+      </c>
+      <c r="F1214" s="8" t="s">
+        <v>4470</v>
+      </c>
+      <c r="G1214" s="1" t="str">
+        <f t="shared" si="37"/>
+        <v>https://mariantoc.github.io/fields.html#PratoJ2026</v>
       </c>
     </row>
     <row r="1215" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1215" s="7" t="s">
-        <v>4315</v>
+      <c r="A1215">
+        <f t="shared" si="38"/>
+        <v>1214</v>
+      </c>
+      <c r="B1215" t="s">
+        <v>4454</v>
+      </c>
+      <c r="C1215" t="s">
+        <v>1570</v>
+      </c>
+      <c r="D1215">
+        <v>2026</v>
+      </c>
+      <c r="E1215" t="s">
+        <v>4455</v>
+      </c>
+      <c r="F1215" s="8" t="s">
+        <v>4471</v>
+      </c>
+      <c r="G1215" s="1" t="str">
+        <f t="shared" si="37"/>
+        <v>https://mariantoc.github.io/topics.html#GoddardDA2026</v>
       </c>
     </row>
     <row r="1216" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1216" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1217" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1217" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1218" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1218" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1219" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1219" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1220" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1220" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1221" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="A1216">
+        <f t="shared" si="38"/>
+        <v>1215</v>
+      </c>
+      <c r="B1216" t="s">
+        <v>4456</v>
+      </c>
+      <c r="C1216" t="s">
+        <v>4457</v>
+      </c>
+      <c r="D1216">
+        <v>2022</v>
+      </c>
+      <c r="E1216" t="s">
+        <v>4458</v>
+      </c>
+      <c r="F1216" s="8" t="s">
+        <v>4472</v>
+      </c>
+      <c r="G1216" s="1" t="str">
+        <f t="shared" ref="G1216:G1220" si="39">HYPERLINK(F1216)</f>
+        <v>https://mariantoc.github.io/minerals.html#DomenechCetal2022</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1217">
+        <f t="shared" ref="A1217:A1220" si="40">A1216+1</f>
+        <v>1216</v>
+      </c>
+      <c r="B1217" t="s">
+        <v>4459</v>
+      </c>
+      <c r="C1217" t="s">
+        <v>4460</v>
+      </c>
+      <c r="D1217">
+        <v>2009</v>
+      </c>
+      <c r="E1217" t="s">
+        <v>4461</v>
+      </c>
+      <c r="F1217" s="8" t="s">
+        <v>4473</v>
+      </c>
+      <c r="G1217" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/fields.html#SchenkCJetal2009</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1218">
+        <f t="shared" si="40"/>
+        <v>1217</v>
+      </c>
+      <c r="B1218" t="s">
+        <v>4462</v>
+      </c>
+      <c r="C1218" t="s">
+        <v>4463</v>
+      </c>
+      <c r="D1218">
+        <v>1945</v>
+      </c>
+      <c r="E1218" t="s">
+        <v>4464</v>
+      </c>
+      <c r="F1218" s="8" t="s">
+        <v>4474</v>
+      </c>
+      <c r="G1218" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/biography.html#BitterliPBaselB1945</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1219">
+        <f t="shared" si="40"/>
+        <v>1218</v>
+      </c>
+      <c r="B1219" t="s">
+        <v>4465</v>
+      </c>
+      <c r="C1219" t="s">
+        <v>4466</v>
+      </c>
+      <c r="D1219">
+        <v>1977</v>
+      </c>
+      <c r="E1219" t="s">
+        <v>4433</v>
+      </c>
+      <c r="F1219" s="8" t="s">
+        <v>4475</v>
+      </c>
+      <c r="G1219" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/speleology.html#PerezW1977</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1220">
+        <f t="shared" si="40"/>
+        <v>1219</v>
+      </c>
+      <c r="B1220" t="s">
+        <v>4467</v>
+      </c>
+      <c r="C1220" t="s">
+        <v>4468</v>
+      </c>
+      <c r="D1220">
+        <v>2005</v>
+      </c>
+      <c r="E1220" t="s">
+        <v>4469</v>
+      </c>
+      <c r="F1220" s="8" t="s">
+        <v>4476</v>
+      </c>
+      <c r="G1220" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#MacsotayOPerazaT2005</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1221" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1222" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1222" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1223" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1223" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1224" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1224" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1225" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1225" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1226" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1226" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1227" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1227" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1228" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1228" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1229" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1229" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1230" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1230" s="7" t="s">
         <v>4315</v>
       </c>

--- a/NotasGeologiaPublicationList_Updated.xlsx
+++ b/NotasGeologiaPublicationList_Updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\mariantoc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4FA6468-5279-453C-A7A1-452AAB831761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F16CBCA3-2709-419A-ADF1-9C7731F91A6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4860" uniqueCount="4477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4918" uniqueCount="4503">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -13758,6 +13758,84 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/stratigraphy.html#MacsotayOPerazaT2005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integración geológica de la Península de Paria, Estado Sucre, Venezuela. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petrash, D.; Revanales, C. </t>
+  </si>
+  <si>
+    <t>Trabajo Especial de Grado presentado ante la ilustre Universidad Central de Venezuela, para optar al título de Ingeniero Geólogo, Caracas, Junio 2006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solución al rompecabezas del origen del Golfo de México – Golfo de América, durante la rotura de la Pangaea, hace 200 millones de años. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edinson Alvarez </t>
+  </si>
+  <si>
+    <t>MAYA, Revista de Geociencias 2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excursión geológica Quebrada La Ge. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shweighauser, J.; Boomer, A. J. </t>
+  </si>
+  <si>
+    <t>III Congreso Geológico Venezolano, Compaňía Shell de Venezuela, 30 de Noviembre de 1959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rocas Paleozoicas en el sector Cerro Negro, Faja Petrolífera del Orinoco, Estado Monagas. </t>
+  </si>
+  <si>
+    <t>Jam, P.; Santos, A. 1988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Icnología de las formaciones Neogeno – Cuaternarias en Venezuela nororiental. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Padrón, V.; Rey, O.; Zapata, E.; Estévez, J. A. </t>
+  </si>
+  <si>
+    <t>Boletín de la Sociedad Venezolana de Geólogos, Volumen 25, Número 2, pp. 23 – 31, 2000</t>
+  </si>
+  <si>
+    <t>Historia de la conquista y población de la Provincia de Venezuela.</t>
+  </si>
+  <si>
+    <t>José de Oviedo y Baňos</t>
+  </si>
+  <si>
+    <t>Biblioteca Ayacucho. Edición Tomás Eloy Martínez; Prólogo Tomás Eloy Martínez y Susana Rotker; Motas por Alicia Ríos; Cronología por Tomás Eloy Martínez; Bibliografía por Tomás Eloy Martínez y Alicia Ríos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huellas problemáticas y su valor paleoecológico en Venezuela. </t>
+  </si>
+  <si>
+    <t>Revista GEOS, Número 16, Junio 1967</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#PetrashDRevanalesC2006</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/topics.html#AlvarezE2026a</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/excursions.html#ShweighauserJBoomerAJ1959</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#JamPSantosA1988</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#PadronVetal2000</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#OviedoJ1992</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#MacsotayO1967</t>
   </si>
 </sst>
 </file>
@@ -14166,7 +14244,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B496A77-4B74-49B4-B08F-A7274E320005}">
-  <dimension ref="A1:H1230"/>
+  <dimension ref="A1:H1267"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="66.5546875" customWidth="1"/>
@@ -44390,7 +44468,7 @@
       <c r="E1214" t="s">
         <v>4439</v>
       </c>
-      <c r="F1214" s="8" t="s">
+      <c r="F1214" t="s">
         <v>4470</v>
       </c>
       <c r="G1214" s="1" t="str">
@@ -44415,7 +44493,7 @@
       <c r="E1215" t="s">
         <v>4455</v>
       </c>
-      <c r="F1215" s="8" t="s">
+      <c r="F1215" t="s">
         <v>4471</v>
       </c>
       <c r="G1215" s="1" t="str">
@@ -44440,17 +44518,17 @@
       <c r="E1216" t="s">
         <v>4458</v>
       </c>
-      <c r="F1216" s="8" t="s">
+      <c r="F1216" t="s">
         <v>4472</v>
       </c>
       <c r="G1216" s="1" t="str">
-        <f t="shared" ref="G1216:G1220" si="39">HYPERLINK(F1216)</f>
+        <f t="shared" ref="G1216:G1230" si="39">HYPERLINK(F1216)</f>
         <v>https://mariantoc.github.io/minerals.html#DomenechCetal2022</v>
       </c>
     </row>
     <row r="1217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1217">
-        <f t="shared" ref="A1217:A1220" si="40">A1216+1</f>
+        <f t="shared" ref="A1217:A1227" si="40">A1216+1</f>
         <v>1216</v>
       </c>
       <c r="B1217" t="s">
@@ -44465,7 +44543,7 @@
       <c r="E1217" t="s">
         <v>4461</v>
       </c>
-      <c r="F1217" s="8" t="s">
+      <c r="F1217" t="s">
         <v>4473</v>
       </c>
       <c r="G1217" s="1" t="str">
@@ -44490,7 +44568,7 @@
       <c r="E1218" t="s">
         <v>4464</v>
       </c>
-      <c r="F1218" s="8" t="s">
+      <c r="F1218" t="s">
         <v>4474</v>
       </c>
       <c r="G1218" s="1" t="str">
@@ -44515,7 +44593,7 @@
       <c r="E1219" t="s">
         <v>4433</v>
       </c>
-      <c r="F1219" s="8" t="s">
+      <c r="F1219" t="s">
         <v>4475</v>
       </c>
       <c r="G1219" s="1" t="str">
@@ -44540,7 +44618,7 @@
       <c r="E1220" t="s">
         <v>4469</v>
       </c>
-      <c r="F1220" s="8" t="s">
+      <c r="F1220" t="s">
         <v>4476</v>
       </c>
       <c r="G1220" s="1" t="str">
@@ -44549,52 +44627,380 @@
       </c>
     </row>
     <row r="1221" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1221" s="7" t="s">
-        <v>4315</v>
+      <c r="A1221">
+        <f t="shared" si="40"/>
+        <v>1220</v>
+      </c>
+      <c r="B1221" t="s">
+        <v>4477</v>
+      </c>
+      <c r="C1221" t="s">
+        <v>4478</v>
+      </c>
+      <c r="D1221">
+        <v>2006</v>
+      </c>
+      <c r="E1221" t="s">
+        <v>4479</v>
+      </c>
+      <c r="F1221" s="8" t="s">
+        <v>4496</v>
+      </c>
+      <c r="G1221" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#PetrashDRevanalesC2006</v>
       </c>
     </row>
     <row r="1222" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1222" s="7" t="s">
-        <v>4315</v>
+      <c r="A1222">
+        <f t="shared" si="40"/>
+        <v>1221</v>
+      </c>
+      <c r="B1222" t="s">
+        <v>4480</v>
+      </c>
+      <c r="C1222" t="s">
+        <v>4481</v>
+      </c>
+      <c r="D1222">
+        <v>2026</v>
+      </c>
+      <c r="E1222" t="s">
+        <v>4482</v>
+      </c>
+      <c r="F1222" s="8" t="s">
+        <v>4497</v>
+      </c>
+      <c r="G1222" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/topics.html#AlvarezE2026a</v>
       </c>
     </row>
     <row r="1223" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1223" s="7" t="s">
-        <v>4315</v>
+      <c r="A1223">
+        <f t="shared" si="40"/>
+        <v>1222</v>
+      </c>
+      <c r="B1223" t="s">
+        <v>4483</v>
+      </c>
+      <c r="C1223" t="s">
+        <v>4484</v>
+      </c>
+      <c r="D1223">
+        <v>1959</v>
+      </c>
+      <c r="E1223" t="s">
+        <v>4485</v>
+      </c>
+      <c r="F1223" s="8" t="s">
+        <v>4498</v>
+      </c>
+      <c r="G1223" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/excursions.html#ShweighauserJBoomerAJ1959</v>
       </c>
     </row>
     <row r="1224" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1224" s="7" t="s">
-        <v>4315</v>
+      <c r="A1224">
+        <f t="shared" si="40"/>
+        <v>1223</v>
+      </c>
+      <c r="B1224" t="s">
+        <v>4486</v>
+      </c>
+      <c r="C1224" t="s">
+        <v>4487</v>
+      </c>
+      <c r="D1224">
+        <v>1988</v>
+      </c>
+      <c r="E1224" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F1224" s="8" t="s">
+        <v>4499</v>
+      </c>
+      <c r="G1224" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#JamPSantosA1988</v>
       </c>
     </row>
     <row r="1225" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1225" s="7" t="s">
-        <v>4315</v>
+      <c r="A1225">
+        <f t="shared" si="40"/>
+        <v>1224</v>
+      </c>
+      <c r="B1225" t="s">
+        <v>4488</v>
+      </c>
+      <c r="C1225" t="s">
+        <v>4489</v>
+      </c>
+      <c r="D1225">
+        <v>2000</v>
+      </c>
+      <c r="E1225" t="s">
+        <v>4490</v>
+      </c>
+      <c r="F1225" s="8" t="s">
+        <v>4500</v>
+      </c>
+      <c r="G1225" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#PadronVetal2000</v>
       </c>
     </row>
     <row r="1226" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1226" s="7" t="s">
-        <v>4315</v>
+      <c r="A1226">
+        <f t="shared" si="40"/>
+        <v>1225</v>
+      </c>
+      <c r="B1226" t="s">
+        <v>4491</v>
+      </c>
+      <c r="C1226" t="s">
+        <v>4492</v>
+      </c>
+      <c r="D1226">
+        <v>1992</v>
+      </c>
+      <c r="E1226" t="s">
+        <v>4493</v>
+      </c>
+      <c r="F1226" s="8" t="s">
+        <v>4501</v>
+      </c>
+      <c r="G1226" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/biography.html#OviedoJ1992</v>
       </c>
     </row>
     <row r="1227" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1227" s="7" t="s">
-        <v>4315</v>
+      <c r="A1227">
+        <f t="shared" si="40"/>
+        <v>1226</v>
+      </c>
+      <c r="B1227" t="s">
+        <v>4494</v>
+      </c>
+      <c r="C1227" t="s">
+        <v>2239</v>
+      </c>
+      <c r="D1227">
+        <v>1967</v>
+      </c>
+      <c r="E1227" t="s">
+        <v>4495</v>
+      </c>
+      <c r="F1227" s="8" t="s">
+        <v>4502</v>
+      </c>
+      <c r="G1227" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#MacsotayO1967</v>
       </c>
     </row>
     <row r="1228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1228" s="7" t="s">
         <v>4315</v>
       </c>
+      <c r="G1228" s="1"/>
     </row>
     <row r="1229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1229" s="7" t="s">
         <v>4315</v>
       </c>
+      <c r="G1229" s="1"/>
     </row>
     <row r="1230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1230" s="7" t="s">
+        <v>4315</v>
+      </c>
+      <c r="G1230" s="1"/>
+    </row>
+    <row r="1231" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F1231" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F1232" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1233" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1233" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1234" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1234" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1235" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1235" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1236" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1236" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1237" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1237" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1238" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1238" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1239" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1239" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1240" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1240" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1241" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1241" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1242" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1242" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1243" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1243" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1244" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1244" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1245" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1245" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1246" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1246" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1247" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1247" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1248" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1248" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1249" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1249" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1250" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1250" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1251" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1251" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1252" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1252" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1253" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1253" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1254" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1254" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1255" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1255" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1256" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1256" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1257" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1257" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1258" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1258" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1259" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1259" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1260" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1260" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1261" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1261" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1262" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1262" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1263" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1263" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1264" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1264" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1265" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1265" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1266" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1266" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1267" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1267" s="7" t="s">
         <v>4315</v>
       </c>
     </row>

--- a/NotasGeologiaPublicationList_Updated.xlsx
+++ b/NotasGeologiaPublicationList_Updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\mariantoc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F16CBCA3-2709-419A-ADF1-9C7731F91A6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B20F3F74-86ED-45FD-BF5E-758ACCC5026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4918" uniqueCount="4503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4930" uniqueCount="4517">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -13836,6 +13836,48 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/stratigraphy.html#MacsotayO1967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Análisis del shale oil y Venezuela. Historia, actualidad y futuro de la producción de yacimientos no convencionales en USA e impacto en la recuperación de la industria petrolera venezolana. </t>
+  </si>
+  <si>
+    <t>Julián Salazar</t>
+  </si>
+  <si>
+    <t>Tomado del perfil de LinkedIn de Julián Andrés Salazar Vásquez, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avances de la Inteligencia Artificial aplicada al nannoplancton calcáreo. </t>
+  </si>
+  <si>
+    <t>MAYA, Revista de Geociencias, Abril 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moritz Blumenthal, geólogo petrolero y andinista. </t>
+  </si>
+  <si>
+    <t>MAYA. Revista de Geociencias, Abril 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resumen de la charla sobre el modelo sedimentológico del Miembro Inferior de la Formación Lagunillas, en los Bloques III y IV, en el área centro oriental del Lago de Maracaibo. </t>
+  </si>
+  <si>
+    <t>Lizaveta Terán y Omar Colmenares</t>
+  </si>
+  <si>
+    <t>Maraven S.A., Caracas, Venezuela, 6 de Agosto de 1987</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/fields.html#SalazarJ2026</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#CastroM2026</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#RodriguezJA2026</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#TeranlColmenareso1987</t>
   </si>
 </sst>
 </file>
@@ -44522,13 +44564,13 @@
         <v>4472</v>
       </c>
       <c r="G1216" s="1" t="str">
-        <f t="shared" ref="G1216:G1230" si="39">HYPERLINK(F1216)</f>
+        <f t="shared" ref="G1216:G1231" si="39">HYPERLINK(F1216)</f>
         <v>https://mariantoc.github.io/minerals.html#DomenechCetal2022</v>
       </c>
     </row>
     <row r="1217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1217">
-        <f t="shared" ref="A1217:A1227" si="40">A1216+1</f>
+        <f t="shared" ref="A1217:A1232" si="40">A1216+1</f>
         <v>1216</v>
       </c>
       <c r="B1217" t="s">
@@ -44643,7 +44685,7 @@
       <c r="E1221" t="s">
         <v>4479</v>
       </c>
-      <c r="F1221" s="8" t="s">
+      <c r="F1221" t="s">
         <v>4496</v>
       </c>
       <c r="G1221" s="1" t="str">
@@ -44668,7 +44710,7 @@
       <c r="E1222" t="s">
         <v>4482</v>
       </c>
-      <c r="F1222" s="8" t="s">
+      <c r="F1222" t="s">
         <v>4497</v>
       </c>
       <c r="G1222" s="1" t="str">
@@ -44693,7 +44735,7 @@
       <c r="E1223" t="s">
         <v>4485</v>
       </c>
-      <c r="F1223" s="8" t="s">
+      <c r="F1223" t="s">
         <v>4498</v>
       </c>
       <c r="G1223" s="1" t="str">
@@ -44718,7 +44760,7 @@
       <c r="E1224" t="s">
         <v>1615</v>
       </c>
-      <c r="F1224" s="8" t="s">
+      <c r="F1224" t="s">
         <v>4499</v>
       </c>
       <c r="G1224" s="1" t="str">
@@ -44743,7 +44785,7 @@
       <c r="E1225" t="s">
         <v>4490</v>
       </c>
-      <c r="F1225" s="8" t="s">
+      <c r="F1225" t="s">
         <v>4500</v>
       </c>
       <c r="G1225" s="1" t="str">
@@ -44768,7 +44810,7 @@
       <c r="E1226" t="s">
         <v>4493</v>
       </c>
-      <c r="F1226" s="8" t="s">
+      <c r="F1226" t="s">
         <v>4501</v>
       </c>
       <c r="G1226" s="1" t="str">
@@ -44793,7 +44835,7 @@
       <c r="E1227" t="s">
         <v>4495</v>
       </c>
-      <c r="F1227" s="8" t="s">
+      <c r="F1227" t="s">
         <v>4502</v>
       </c>
       <c r="G1227" s="1" t="str">
@@ -44802,26 +44844,103 @@
       </c>
     </row>
     <row r="1228" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1228" s="7" t="s">
-        <v>4315</v>
-      </c>
-      <c r="G1228" s="1"/>
+      <c r="A1228">
+        <f t="shared" si="40"/>
+        <v>1227</v>
+      </c>
+      <c r="B1228" t="s">
+        <v>4503</v>
+      </c>
+      <c r="C1228" t="s">
+        <v>4504</v>
+      </c>
+      <c r="D1228">
+        <v>2026</v>
+      </c>
+      <c r="E1228" t="s">
+        <v>4505</v>
+      </c>
+      <c r="F1228" s="8" t="s">
+        <v>4513</v>
+      </c>
+      <c r="G1228" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/fields.html#SalazarJ2026</v>
+      </c>
     </row>
     <row r="1229" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1229" s="7" t="s">
-        <v>4315</v>
-      </c>
-      <c r="G1229" s="1"/>
+      <c r="A1229">
+        <f t="shared" si="40"/>
+        <v>1228</v>
+      </c>
+      <c r="B1229" t="s">
+        <v>4506</v>
+      </c>
+      <c r="C1229" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1229">
+        <v>2026</v>
+      </c>
+      <c r="E1229" t="s">
+        <v>4507</v>
+      </c>
+      <c r="F1229" s="8" t="s">
+        <v>4514</v>
+      </c>
+      <c r="G1229" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#CastroM2026</v>
+      </c>
     </row>
     <row r="1230" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1230" s="7" t="s">
-        <v>4315</v>
-      </c>
-      <c r="G1230" s="1"/>
+      <c r="A1230">
+        <f t="shared" si="40"/>
+        <v>1229</v>
+      </c>
+      <c r="B1230" t="s">
+        <v>4508</v>
+      </c>
+      <c r="C1230" t="s">
+        <v>341</v>
+      </c>
+      <c r="D1230">
+        <v>2026</v>
+      </c>
+      <c r="E1230" t="s">
+        <v>4509</v>
+      </c>
+      <c r="F1230" s="8" t="s">
+        <v>4515</v>
+      </c>
+      <c r="G1230" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/biography.html#RodriguezJA2026</v>
+      </c>
     </row>
     <row r="1231" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1231" s="7" t="s">
-        <v>4315</v>
+      <c r="A1231">
+        <f t="shared" si="40"/>
+        <v>1230</v>
+      </c>
+      <c r="B1231" t="s">
+        <v>4510</v>
+      </c>
+      <c r="C1231" t="s">
+        <v>4511</v>
+      </c>
+      <c r="D1231">
+        <v>1987</v>
+      </c>
+      <c r="E1231" t="s">
+        <v>4512</v>
+      </c>
+      <c r="F1231" s="8" t="s">
+        <v>4516</v>
+      </c>
+      <c r="G1231" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#TeranlColmenareso1987</v>
       </c>
     </row>
     <row r="1232" spans="1:7" x14ac:dyDescent="0.3">

--- a/NotasGeologiaPublicationList_Updated.xlsx
+++ b/NotasGeologiaPublicationList_Updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\mariantoc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B20F3F74-86ED-45FD-BF5E-758ACCC5026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{055DA7F9-39D6-476E-AC23-CEA0DAEEA99E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4930" uniqueCount="4517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4950" uniqueCount="4542">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -13878,6 +13878,81 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/stratigraphy.html#TeranlColmenareso1987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel Alejandro Salcedo Rodríguez: Una impresionante trayectoria tanto profesional como docente. Individuo de Número de la Academia Nacional de la Ingeniería y el Hábitat, Venezuela. </t>
+  </si>
+  <si>
+    <t>MAYA. Revista de Geociencias, Suplemento Especial Abril 2026, pp. 14 – 19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inírida Rodríguez Millán: Primera dama egresada como ingeniera geofísica de la ilustre Universidad Central de Venezuela. Miembro Correspondiente Nacional de la Academia Nacional de la Ingeniería y el Hábitat, Venezuela. </t>
+  </si>
+  <si>
+    <t>MAYA. Revista de Geociencias, Suplemento Especial Abril 2026, pp. 7 – 13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pequeño bestiario Paleozoico. Quince animales sorprendentes que existieron mucho antes que los dinosaurios. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rubén Darío Martínez </t>
+  </si>
+  <si>
+    <t>Comodora Rivadavia, Universidad de La Patagonia. EDUPA, 2021. Ilustradora: Julieta Caglianone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dunham’s carbonate rock classification. A Spanish terminology. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicolás Gerardo Muňoz </t>
+  </si>
+  <si>
+    <t>Carbonates and Evaporites, Vol. 5, No. 3, 1988, pp. 65 -66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical report update on the Las Cristinas Project, Bolivar State, Venezuela. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ristorcelli, S.; Spencer, R.; Dyer, T.; Goode, J.; Evans, D.; Josic, L.; Sangam, H.; Jackson, H. </t>
+  </si>
+  <si>
+    <t>Prepared for Crystallex International Corporation, November 7, 2007. Public report at SEDAR, file disclose and search for issuer information in Canada Capital Markets</t>
+  </si>
+  <si>
+    <t>Estudio hidrogeoquímico de algunas manifestaciones termales presentes en Falcón noroccidental, Venezuela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montero, R. L.; Martínez, M.; Meléndez, W.; Garbán, G.; Ramos, F. </t>
+  </si>
+  <si>
+    <t>Boletín de la Sociedad Venezolana de Geólogos, Volumen 27, Número 1, pp. 10 -23, 2002</t>
+  </si>
+  <si>
+    <t>El yaguar en la mira.</t>
+  </si>
+  <si>
+    <t>Carta Ecológica de Lagoven S.A., Noviembre – Diciembre, 1982</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#CastroM2026a</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#CastroM2026</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#MartinezRD2021</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#MunozNG1988</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/minerals.html#RistorelliSetal2007</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/hotsprings.html#MonteroRLetal2002</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/ecology.html#Yaguar1982</t>
   </si>
 </sst>
 </file>
@@ -44564,13 +44639,13 @@
         <v>4472</v>
       </c>
       <c r="G1216" s="1" t="str">
-        <f t="shared" ref="G1216:G1231" si="39">HYPERLINK(F1216)</f>
+        <f t="shared" ref="G1216:G1242" si="39">HYPERLINK(F1216)</f>
         <v>https://mariantoc.github.io/minerals.html#DomenechCetal2022</v>
       </c>
     </row>
     <row r="1217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1217">
-        <f t="shared" ref="A1217:A1232" si="40">A1216+1</f>
+        <f t="shared" ref="A1217:A1238" si="40">A1216+1</f>
         <v>1216</v>
       </c>
       <c r="B1217" t="s">
@@ -44860,7 +44935,7 @@
       <c r="E1228" t="s">
         <v>4505</v>
       </c>
-      <c r="F1228" s="8" t="s">
+      <c r="F1228" t="s">
         <v>4513</v>
       </c>
       <c r="G1228" s="1" t="str">
@@ -44885,7 +44960,7 @@
       <c r="E1229" t="s">
         <v>4507</v>
       </c>
-      <c r="F1229" s="8" t="s">
+      <c r="F1229" t="s">
         <v>4514</v>
       </c>
       <c r="G1229" s="1" t="str">
@@ -44910,7 +44985,7 @@
       <c r="E1230" t="s">
         <v>4509</v>
       </c>
-      <c r="F1230" s="8" t="s">
+      <c r="F1230" t="s">
         <v>4515</v>
       </c>
       <c r="G1230" s="1" t="str">
@@ -44935,7 +45010,7 @@
       <c r="E1231" t="s">
         <v>4512</v>
       </c>
-      <c r="F1231" s="8" t="s">
+      <c r="F1231" t="s">
         <v>4516</v>
       </c>
       <c r="G1231" s="1" t="str">
@@ -44944,86 +45019,227 @@
       </c>
     </row>
     <row r="1232" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1232" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1233" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1233" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1234" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1234" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1235" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1235" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1236" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1236" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1237" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1237" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1238" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1238" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1239" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="A1232">
+        <f t="shared" si="40"/>
+        <v>1231</v>
+      </c>
+      <c r="B1232" t="s">
+        <v>4517</v>
+      </c>
+      <c r="C1232" t="s">
+        <v>2880</v>
+      </c>
+      <c r="D1232">
+        <v>2026</v>
+      </c>
+      <c r="E1232" t="s">
+        <v>4518</v>
+      </c>
+      <c r="F1232" s="8" t="s">
+        <v>4535</v>
+      </c>
+      <c r="G1232" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/biography.html#CastroM2026a</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1233">
+        <f t="shared" si="40"/>
+        <v>1232</v>
+      </c>
+      <c r="B1233" t="s">
+        <v>4519</v>
+      </c>
+      <c r="C1233" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1233">
+        <v>2026</v>
+      </c>
+      <c r="E1233" t="s">
+        <v>4520</v>
+      </c>
+      <c r="F1233" s="8" t="s">
+        <v>4536</v>
+      </c>
+      <c r="G1233" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/biography.html#CastroM2026</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1234">
+        <f t="shared" si="40"/>
+        <v>1233</v>
+      </c>
+      <c r="B1234" t="s">
+        <v>4521</v>
+      </c>
+      <c r="C1234" t="s">
+        <v>4522</v>
+      </c>
+      <c r="D1234">
+        <v>2021</v>
+      </c>
+      <c r="E1234" t="s">
+        <v>4523</v>
+      </c>
+      <c r="F1234" s="8" t="s">
+        <v>4537</v>
+      </c>
+      <c r="G1234" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#MartinezRD2021</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1235">
+        <f t="shared" si="40"/>
+        <v>1234</v>
+      </c>
+      <c r="B1235" t="s">
+        <v>4524</v>
+      </c>
+      <c r="C1235" t="s">
+        <v>4525</v>
+      </c>
+      <c r="D1235">
+        <v>1988</v>
+      </c>
+      <c r="E1235" t="s">
+        <v>4526</v>
+      </c>
+      <c r="F1235" s="8" t="s">
+        <v>4538</v>
+      </c>
+      <c r="G1235" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#MunozNG1988</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1236">
+        <f t="shared" si="40"/>
+        <v>1235</v>
+      </c>
+      <c r="B1236" t="s">
+        <v>4527</v>
+      </c>
+      <c r="C1236" t="s">
+        <v>4528</v>
+      </c>
+      <c r="D1236">
+        <v>2007</v>
+      </c>
+      <c r="E1236" t="s">
+        <v>4529</v>
+      </c>
+      <c r="F1236" s="8" t="s">
+        <v>4539</v>
+      </c>
+      <c r="G1236" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/minerals.html#RistorelliSetal2007</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1237">
+        <f t="shared" si="40"/>
+        <v>1236</v>
+      </c>
+      <c r="B1237" t="s">
+        <v>4530</v>
+      </c>
+      <c r="C1237" t="s">
+        <v>4531</v>
+      </c>
+      <c r="D1237">
+        <v>2002</v>
+      </c>
+      <c r="E1237" t="s">
+        <v>4532</v>
+      </c>
+      <c r="F1237" s="8" t="s">
+        <v>4540</v>
+      </c>
+      <c r="G1237" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/hotsprings.html#MonteroRLetal2002</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1238">
+        <f t="shared" si="40"/>
+        <v>1237</v>
+      </c>
+      <c r="B1238" t="s">
+        <v>4533</v>
+      </c>
+      <c r="D1238">
+        <v>1982</v>
+      </c>
+      <c r="E1238" t="s">
+        <v>4534</v>
+      </c>
+      <c r="F1238" s="8" t="s">
+        <v>4541</v>
+      </c>
+      <c r="G1238" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/ecology.html#Yaguar1982</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1239" s="7" t="s">
         <v>4315</v>
       </c>
-    </row>
-    <row r="1240" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="G1239" s="1"/>
+    </row>
+    <row r="1240" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1240" s="7" t="s">
         <v>4315</v>
       </c>
-    </row>
-    <row r="1241" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="G1240" s="1"/>
+    </row>
+    <row r="1241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1241" s="7" t="s">
         <v>4315</v>
       </c>
-    </row>
-    <row r="1242" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="G1241" s="1"/>
+    </row>
+    <row r="1242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1242" s="7" t="s">
         <v>4315</v>
       </c>
-    </row>
-    <row r="1243" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="G1242" s="1"/>
+    </row>
+    <row r="1243" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1243" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1244" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1244" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1245" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1245" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1246" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1246" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1247" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1247" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1248" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1248" s="7" t="s">
         <v>4315</v>
       </c>

--- a/NotasGeologiaPublicationList_Updated.xlsx
+++ b/NotasGeologiaPublicationList_Updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\mariantoc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{055DA7F9-39D6-476E-AC23-CEA0DAEEA99E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2719CAA0-70BA-4ED3-B97F-DE6F9D520FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4950" uniqueCount="4542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4970" uniqueCount="4567">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -13953,6 +13953,81 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/ecology.html#Yaguar1982</t>
+  </si>
+  <si>
+    <t>El culto al Dios Seth, creó la más antigua colección de fósiles de la historia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appraisal of market value Las Brisas Gold Mining Concessions, Bolivar State, Venezuela. </t>
+  </si>
+  <si>
+    <t>Trevor R. Ellis</t>
+  </si>
+  <si>
+    <t>Tomado de SEDAR, Canada. Ellis International Services Inc., report date: April 17, 2006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El sismo de Caracas de 1900 por Joseph Liechty, Director del Colegio Alemán de Caracas. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">José Antonio Rodríguez </t>
+  </si>
+  <si>
+    <t>MAYA. Revista de Geociencias, Abril 2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diverse Devonian plant assemblages from western Venezuela. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berry, C.; Casas, J.E.; Moody, J. </t>
+  </si>
+  <si>
+    <t>Table Ronde Européenne, Lyon, 7 – 9 Juillet, pp. 3, 1992</t>
+  </si>
+  <si>
+    <t>Parque Nacional Sierra Nevada. Biotipo de características excepcionales.</t>
+  </si>
+  <si>
+    <t>Carta Ecológica de Lagoven S.A. 1981.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guía excursión geológica al Caño Maraca. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ignacio Fierro S. </t>
+  </si>
+  <si>
+    <t>Ministerio de Energía y Minas, División de Exploraciones Geológicas, Maracaibo, Agosto 1983</t>
+  </si>
+  <si>
+    <t>Taller de descripción de rocas carbonáticas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emma Kummerow </t>
+  </si>
+  <si>
+    <t>Lagoven S.A., Departamento de Geología, Gerencia de Estudios Regionales, 1989</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/topics.html#CasasJE2026</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/minerals.html#EllisTR2006</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#RodriguezJA2026a</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#BerryCetal1992</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/ecology.html#SierraNevada1981</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/excursions.html#FierroI1983</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#KummerowE1989</t>
   </si>
 </sst>
 </file>
@@ -44639,13 +44714,13 @@
         <v>4472</v>
       </c>
       <c r="G1216" s="1" t="str">
-        <f t="shared" ref="G1216:G1242" si="39">HYPERLINK(F1216)</f>
+        <f t="shared" ref="G1216:G1246" si="39">HYPERLINK(F1216)</f>
         <v>https://mariantoc.github.io/minerals.html#DomenechCetal2022</v>
       </c>
     </row>
     <row r="1217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1217">
-        <f t="shared" ref="A1217:A1238" si="40">A1216+1</f>
+        <f t="shared" ref="A1217:A1245" si="40">A1216+1</f>
         <v>1216</v>
       </c>
       <c r="B1217" t="s">
@@ -45035,7 +45110,7 @@
       <c r="E1232" t="s">
         <v>4518</v>
       </c>
-      <c r="F1232" s="8" t="s">
+      <c r="F1232" t="s">
         <v>4535</v>
       </c>
       <c r="G1232" s="1" t="str">
@@ -45060,7 +45135,7 @@
       <c r="E1233" t="s">
         <v>4520</v>
       </c>
-      <c r="F1233" s="8" t="s">
+      <c r="F1233" t="s">
         <v>4536</v>
       </c>
       <c r="G1233" s="1" t="str">
@@ -45085,7 +45160,7 @@
       <c r="E1234" t="s">
         <v>4523</v>
       </c>
-      <c r="F1234" s="8" t="s">
+      <c r="F1234" t="s">
         <v>4537</v>
       </c>
       <c r="G1234" s="1" t="str">
@@ -45110,7 +45185,7 @@
       <c r="E1235" t="s">
         <v>4526</v>
       </c>
-      <c r="F1235" s="8" t="s">
+      <c r="F1235" t="s">
         <v>4538</v>
       </c>
       <c r="G1235" s="1" t="str">
@@ -45135,7 +45210,7 @@
       <c r="E1236" t="s">
         <v>4529</v>
       </c>
-      <c r="F1236" s="8" t="s">
+      <c r="F1236" t="s">
         <v>4539</v>
       </c>
       <c r="G1236" s="1" t="str">
@@ -45160,7 +45235,7 @@
       <c r="E1237" t="s">
         <v>4532</v>
       </c>
-      <c r="F1237" s="8" t="s">
+      <c r="F1237" t="s">
         <v>4540</v>
       </c>
       <c r="G1237" s="1" t="str">
@@ -45182,7 +45257,7 @@
       <c r="E1238" t="s">
         <v>4534</v>
       </c>
-      <c r="F1238" s="8" t="s">
+      <c r="F1238" t="s">
         <v>4541</v>
       </c>
       <c r="G1238" s="1" t="str">
@@ -45191,48 +45266,182 @@
       </c>
     </row>
     <row r="1239" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1239" s="7" t="s">
-        <v>4315</v>
-      </c>
-      <c r="G1239" s="1"/>
+      <c r="A1239">
+        <f t="shared" si="40"/>
+        <v>1238</v>
+      </c>
+      <c r="B1239" t="s">
+        <v>4542</v>
+      </c>
+      <c r="C1239" t="s">
+        <v>2451</v>
+      </c>
+      <c r="D1239">
+        <v>2026</v>
+      </c>
+      <c r="E1239" t="s">
+        <v>4509</v>
+      </c>
+      <c r="F1239" s="8" t="s">
+        <v>4560</v>
+      </c>
+      <c r="G1239" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/topics.html#CasasJE2026</v>
+      </c>
     </row>
     <row r="1240" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1240" s="7" t="s">
-        <v>4315</v>
-      </c>
-      <c r="G1240" s="1"/>
+      <c r="A1240">
+        <f t="shared" si="40"/>
+        <v>1239</v>
+      </c>
+      <c r="B1240" t="s">
+        <v>4543</v>
+      </c>
+      <c r="C1240" t="s">
+        <v>4544</v>
+      </c>
+      <c r="D1240">
+        <v>2006</v>
+      </c>
+      <c r="E1240" t="s">
+        <v>4545</v>
+      </c>
+      <c r="F1240" s="8" t="s">
+        <v>4561</v>
+      </c>
+      <c r="G1240" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/minerals.html#EllisTR2006</v>
+      </c>
     </row>
     <row r="1241" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1241" s="7" t="s">
-        <v>4315</v>
-      </c>
-      <c r="G1241" s="1"/>
+      <c r="A1241">
+        <f t="shared" si="40"/>
+        <v>1240</v>
+      </c>
+      <c r="B1241" t="s">
+        <v>4546</v>
+      </c>
+      <c r="C1241" t="s">
+        <v>4547</v>
+      </c>
+      <c r="D1241">
+        <v>2026</v>
+      </c>
+      <c r="E1241" t="s">
+        <v>4548</v>
+      </c>
+      <c r="F1241" s="8" t="s">
+        <v>4562</v>
+      </c>
+      <c r="G1241" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/biography.html#RodriguezJA2026a</v>
+      </c>
     </row>
     <row r="1242" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1242" s="7" t="s">
-        <v>4315</v>
-      </c>
-      <c r="G1242" s="1"/>
+      <c r="A1242">
+        <f t="shared" si="40"/>
+        <v>1241</v>
+      </c>
+      <c r="B1242" t="s">
+        <v>4549</v>
+      </c>
+      <c r="C1242" t="s">
+        <v>4550</v>
+      </c>
+      <c r="D1242">
+        <v>1992</v>
+      </c>
+      <c r="E1242" t="s">
+        <v>4551</v>
+      </c>
+      <c r="F1242" s="8" t="s">
+        <v>4563</v>
+      </c>
+      <c r="G1242" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#BerryCetal1992</v>
+      </c>
     </row>
     <row r="1243" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1243" s="7" t="s">
-        <v>4315</v>
+      <c r="A1243">
+        <f t="shared" si="40"/>
+        <v>1242</v>
+      </c>
+      <c r="B1243" t="s">
+        <v>4552</v>
+      </c>
+      <c r="D1243">
+        <v>1981</v>
+      </c>
+      <c r="E1243" t="s">
+        <v>4553</v>
+      </c>
+      <c r="F1243" s="8" t="s">
+        <v>4564</v>
+      </c>
+      <c r="G1243" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/ecology.html#SierraNevada1981</v>
       </c>
     </row>
     <row r="1244" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1244" s="7" t="s">
-        <v>4315</v>
+      <c r="A1244">
+        <f t="shared" si="40"/>
+        <v>1243</v>
+      </c>
+      <c r="B1244" t="s">
+        <v>4554</v>
+      </c>
+      <c r="C1244" t="s">
+        <v>4555</v>
+      </c>
+      <c r="D1244">
+        <v>1983</v>
+      </c>
+      <c r="E1244" t="s">
+        <v>4556</v>
+      </c>
+      <c r="F1244" s="8" t="s">
+        <v>4565</v>
+      </c>
+      <c r="G1244" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/excursions.html#FierroI1983</v>
       </c>
     </row>
     <row r="1245" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1245" s="7" t="s">
-        <v>4315</v>
+      <c r="A1245">
+        <f t="shared" si="40"/>
+        <v>1244</v>
+      </c>
+      <c r="B1245" t="s">
+        <v>4557</v>
+      </c>
+      <c r="C1245" t="s">
+        <v>4558</v>
+      </c>
+      <c r="D1245">
+        <v>1989</v>
+      </c>
+      <c r="E1245" t="s">
+        <v>4559</v>
+      </c>
+      <c r="F1245" s="8" t="s">
+        <v>4566</v>
+      </c>
+      <c r="G1245" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#KummerowE1989</v>
       </c>
     </row>
     <row r="1246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1246" s="7" t="s">
         <v>4315</v>
       </c>
+      <c r="G1246" s="1"/>
     </row>
     <row r="1247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1247" s="7" t="s">

--- a/NotasGeologiaPublicationList_Updated.xlsx
+++ b/NotasGeologiaPublicationList_Updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\mariantoc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2719CAA0-70BA-4ED3-B97F-DE6F9D520FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7DCBF48-48B6-4F4F-8973-DF854970C109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4970" uniqueCount="4567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4991" uniqueCount="4595">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -14028,6 +14028,90 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/stratigraphy.html#KummerowE1989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical report 43-101 on The Siembra Minera Project, Bolivar State, Venezuela. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lambert, R. J.; Miranda, H.; Texidor Carlson , J.; Altman, K.A.; Malensek, G.A. </t>
+  </si>
+  <si>
+    <t>Tomado de SEDAR, Canada. RPA, Rock Solid Resources, March 16, 2018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The diamond fields of Venezuela. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">John C. Davey </t>
+  </si>
+  <si>
+    <t>Barncoose Terrace, Redruth, Cornwall, England, 1948. Engineering and Mining</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Algunos fósiles Ordovícicos de la Formación Caparo (Estado Barinas, Andes de Venezuela). </t>
+  </si>
+  <si>
+    <t>Gutiérrez Marco, J. C.; Odreman Rivas, O. E.; Rabano, I.; Villas, E.</t>
+  </si>
+  <si>
+    <t>Table Ronde Européenne, Lyon, France, pp. 27, 7 – 9 Julliet, 1992</t>
+  </si>
+  <si>
+    <t>The Bocono Fault, Western Venezuela.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schubert, C.; Estévez, R.; Henneberg, H. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Qué cantidad de agua tiene el país? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oscar González Pozo </t>
+  </si>
+  <si>
+    <t>Carta Ecológica de Lagoven S.A., Número 42, Mayo – Junio, 1988</t>
+  </si>
+  <si>
+    <t>Annales Tectonicae, Special Issue, Supplement to Volume VI, pp. 238 – 260, 1992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tertulia con Antonio Francés. Nuestro desarrollo no será posible sin el rescate moral del país. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gustavo Romero León </t>
+  </si>
+  <si>
+    <t>Revista Nosotros, Lagoven S.A., Noviembre 1990</t>
+  </si>
+  <si>
+    <t>Introducción a los Tintínidos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mario Trejo </t>
+  </si>
+  <si>
+    <t>Curso de Micropaleontología Aplicada, Universidad Autónoma de México, Instituto de Geología, Octubre 6 – 26, 1980</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/minerals.html#LambertRJetal2018</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/minerals.html#DaveyJC1948</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#GutierrezMetal1992</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/structural.html#SchubertCetal1992</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/ecology.html#GonzalezO1988</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#RomeroC1990</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#TrejoM1980</t>
   </si>
 </sst>
 </file>
@@ -44714,13 +44798,13 @@
         <v>4472</v>
       </c>
       <c r="G1216" s="1" t="str">
-        <f t="shared" ref="G1216:G1246" si="39">HYPERLINK(F1216)</f>
+        <f t="shared" ref="G1216:G1252" si="39">HYPERLINK(F1216)</f>
         <v>https://mariantoc.github.io/minerals.html#DomenechCetal2022</v>
       </c>
     </row>
     <row r="1217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1217">
-        <f t="shared" ref="A1217:A1245" si="40">A1216+1</f>
+        <f t="shared" ref="A1217:A1252" si="40">A1216+1</f>
         <v>1216</v>
       </c>
       <c r="B1217" t="s">
@@ -45282,7 +45366,7 @@
       <c r="E1239" t="s">
         <v>4509</v>
       </c>
-      <c r="F1239" s="8" t="s">
+      <c r="F1239" t="s">
         <v>4560</v>
       </c>
       <c r="G1239" s="1" t="str">
@@ -45307,7 +45391,7 @@
       <c r="E1240" t="s">
         <v>4545</v>
       </c>
-      <c r="F1240" s="8" t="s">
+      <c r="F1240" t="s">
         <v>4561</v>
       </c>
       <c r="G1240" s="1" t="str">
@@ -45332,7 +45416,7 @@
       <c r="E1241" t="s">
         <v>4548</v>
       </c>
-      <c r="F1241" s="8" t="s">
+      <c r="F1241" t="s">
         <v>4562</v>
       </c>
       <c r="G1241" s="1" t="str">
@@ -45357,7 +45441,7 @@
       <c r="E1242" t="s">
         <v>4551</v>
       </c>
-      <c r="F1242" s="8" t="s">
+      <c r="F1242" t="s">
         <v>4563</v>
       </c>
       <c r="G1242" s="1" t="str">
@@ -45379,7 +45463,7 @@
       <c r="E1243" t="s">
         <v>4553</v>
       </c>
-      <c r="F1243" s="8" t="s">
+      <c r="F1243" t="s">
         <v>4564</v>
       </c>
       <c r="G1243" s="1" t="str">
@@ -45404,7 +45488,7 @@
       <c r="E1244" t="s">
         <v>4556</v>
       </c>
-      <c r="F1244" s="8" t="s">
+      <c r="F1244" t="s">
         <v>4565</v>
       </c>
       <c r="G1244" s="1" t="str">
@@ -45429,7 +45513,7 @@
       <c r="E1245" t="s">
         <v>4559</v>
       </c>
-      <c r="F1245" s="8" t="s">
+      <c r="F1245" t="s">
         <v>4566</v>
       </c>
       <c r="G1245" s="1" t="str">
@@ -45438,97 +45522,236 @@
       </c>
     </row>
     <row r="1246" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1246" s="7" t="s">
-        <v>4315</v>
-      </c>
-      <c r="G1246" s="1"/>
+      <c r="A1246">
+        <f t="shared" si="40"/>
+        <v>1245</v>
+      </c>
+      <c r="B1246" t="s">
+        <v>4567</v>
+      </c>
+      <c r="C1246" t="s">
+        <v>4568</v>
+      </c>
+      <c r="D1246">
+        <v>2018</v>
+      </c>
+      <c r="E1246" t="s">
+        <v>4569</v>
+      </c>
+      <c r="F1246" s="8" t="s">
+        <v>4588</v>
+      </c>
+      <c r="G1246" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/minerals.html#LambertRJetal2018</v>
+      </c>
     </row>
     <row r="1247" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1247" s="7" t="s">
-        <v>4315</v>
+      <c r="A1247">
+        <f t="shared" si="40"/>
+        <v>1246</v>
+      </c>
+      <c r="B1247" t="s">
+        <v>4570</v>
+      </c>
+      <c r="C1247" t="s">
+        <v>4571</v>
+      </c>
+      <c r="D1247">
+        <v>1948</v>
+      </c>
+      <c r="E1247" t="s">
+        <v>4572</v>
+      </c>
+      <c r="F1247" s="8" t="s">
+        <v>4589</v>
+      </c>
+      <c r="G1247" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/minerals.html#DaveyJC1948</v>
       </c>
     </row>
     <row r="1248" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1248" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1249" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1249" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1250" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1250" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1251" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1251" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1252" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1252" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1253" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="A1248">
+        <f t="shared" si="40"/>
+        <v>1247</v>
+      </c>
+      <c r="B1248" t="s">
+        <v>4573</v>
+      </c>
+      <c r="C1248" t="s">
+        <v>4574</v>
+      </c>
+      <c r="D1248">
+        <v>1992</v>
+      </c>
+      <c r="E1248" t="s">
+        <v>4575</v>
+      </c>
+      <c r="F1248" s="8" t="s">
+        <v>4590</v>
+      </c>
+      <c r="G1248" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#GutierrezMetal1992</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1249">
+        <f t="shared" si="40"/>
+        <v>1248</v>
+      </c>
+      <c r="B1249" t="s">
+        <v>4576</v>
+      </c>
+      <c r="C1249" t="s">
+        <v>4577</v>
+      </c>
+      <c r="D1249">
+        <v>1992</v>
+      </c>
+      <c r="E1249" t="s">
+        <v>4581</v>
+      </c>
+      <c r="F1249" s="8" t="s">
+        <v>4591</v>
+      </c>
+      <c r="G1249" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/structural.html#SchubertCetal1992</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1250">
+        <f t="shared" si="40"/>
+        <v>1249</v>
+      </c>
+      <c r="B1250" t="s">
+        <v>4578</v>
+      </c>
+      <c r="C1250" t="s">
+        <v>4579</v>
+      </c>
+      <c r="D1250">
+        <v>1988</v>
+      </c>
+      <c r="E1250" t="s">
+        <v>4580</v>
+      </c>
+      <c r="F1250" s="8" t="s">
+        <v>4592</v>
+      </c>
+      <c r="G1250" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/ecology.html#GonzalezO1988</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1251">
+        <f t="shared" si="40"/>
+        <v>1250</v>
+      </c>
+      <c r="B1251" t="s">
+        <v>4582</v>
+      </c>
+      <c r="C1251" t="s">
+        <v>4583</v>
+      </c>
+      <c r="D1251">
+        <v>1990</v>
+      </c>
+      <c r="E1251" t="s">
+        <v>4584</v>
+      </c>
+      <c r="F1251" s="8" t="s">
+        <v>4593</v>
+      </c>
+      <c r="G1251" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/biography.html#RomeroC1990</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1252">
+        <f t="shared" si="40"/>
+        <v>1251</v>
+      </c>
+      <c r="B1252" t="s">
+        <v>4585</v>
+      </c>
+      <c r="C1252" t="s">
+        <v>4586</v>
+      </c>
+      <c r="D1252">
+        <v>1980</v>
+      </c>
+      <c r="E1252" t="s">
+        <v>4587</v>
+      </c>
+      <c r="F1252" s="8" t="s">
+        <v>4594</v>
+      </c>
+      <c r="G1252" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#TrejoM1980</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1253" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1254" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1254" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1254" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1255" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1255" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1255" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1256" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1256" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1256" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1257" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1257" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1257" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1258" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1258" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1258" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1259" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1259" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1259" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1260" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1260" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1260" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1261" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1261" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1261" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1262" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1262" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1262" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1263" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1263" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1263" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1264" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1264" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1264" s="7" t="s">
         <v>4315</v>
       </c>

--- a/NotasGeologiaPublicationList_Updated.xlsx
+++ b/NotasGeologiaPublicationList_Updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\mariantoc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7DCBF48-48B6-4F4F-8973-DF854970C109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{442C7328-321C-4984-AD76-800E2FAAC76D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$1171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$1267</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4991" uniqueCount="4595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5040" uniqueCount="4623">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -14112,6 +14112,90 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/stratigraphy.html#TrejoM1980</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Report 43 – 101. Rusoro Mining, feasibility study expansion of gold production at Choco – 10 and Incredible – 6, Bolívar State, Venezuela. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Makepeace, D.; Friedman, D.; Anderson, D.; Gowans, R.; Lane, G.; Jacobs, C. </t>
+  </si>
+  <si>
+    <t>Tomado de SEDAR, Canadá. Micon International Limited, mineral industry consultants, December 2011</t>
+  </si>
+  <si>
+    <t>Venezuela.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Otto Renz </t>
+  </si>
+  <si>
+    <t>In: Aspects of Mid-Cretaceous Regional Geology. R. A. Raymond &amp; P. Bengloan. Academic Press, London, 1981</t>
+  </si>
+  <si>
+    <t>Reservas forestales, fuente inagotable de recursos. Cuanto le cuesta a la naturaleza formar un árbol.</t>
+  </si>
+  <si>
+    <t>Walter Zimmermann</t>
+  </si>
+  <si>
+    <t>Carta Ecológica de Lagoven S. A., Número 42, Mayo – Junio, 1988</t>
+  </si>
+  <si>
+    <t>Herodoto: Historiador, etnógrafo, geografo y ¿geólogo?</t>
+  </si>
+  <si>
+    <t>Jhonny Edgar Casas</t>
+  </si>
+  <si>
+    <t>Boletín de la Academia de Ciencias Físicas, Matemáticas y Naturales, Volumen LXXXV, Número 2, 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Efectos contaminantes de aditivos de perforación en estudios de petrografía orgánica. </t>
+  </si>
+  <si>
+    <t>Nidya Jordan</t>
+  </si>
+  <si>
+    <t>Revista Técnica de Intevep, Volumen 3, Número 2, pp. 161 – 166, 1983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evolución tectonoestratigráfica de la Serranía del Interior y de la Subcuenca de Maturín. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subieta, T.; Carnevalli, J.; Hunter, V. </t>
+  </si>
+  <si>
+    <t>III Simposio Bolivariano de Exploración Petrolera de las Cuencas Subandinas, Caracas 13 – 16 de Marzo de 1988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curso de geodinámica y tectónica. Guía de campo, región nororiental de Venezuela. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chevalier, I.; Rossi, T.; Hernández, G.; Quintero, M. </t>
+  </si>
+  <si>
+    <t>Lagoven S. A. Edición revisada en Febrero de 1985 por Gilbert Pottier, Pierre Jacout, Gustavo Hernández y Tomás Subieta</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/minerals.html#MakepeaceDetal2011</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#RenzO1981</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/topics.html#CasasJE2025g</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/ecology.html#ZimmermannW1988</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/geochemistry.html#JordanN1983</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/structural.html#SubietaTetal1988</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/excursions.html#ChevalierIetal1985</t>
   </si>
 </sst>
 </file>
@@ -14520,7 +14604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B496A77-4B74-49B4-B08F-A7274E320005}">
-  <dimension ref="A1:H1267"/>
+  <dimension ref="A1:H1295"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="66.5546875" customWidth="1"/>
@@ -44798,13 +44882,13 @@
         <v>4472</v>
       </c>
       <c r="G1216" s="1" t="str">
-        <f t="shared" ref="G1216:G1252" si="39">HYPERLINK(F1216)</f>
+        <f t="shared" ref="G1216:G1259" si="39">HYPERLINK(F1216)</f>
         <v>https://mariantoc.github.io/minerals.html#DomenechCetal2022</v>
       </c>
     </row>
     <row r="1217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1217">
-        <f t="shared" ref="A1217:A1252" si="40">A1216+1</f>
+        <f t="shared" ref="A1217:A1259" si="40">A1216+1</f>
         <v>1216</v>
       </c>
       <c r="B1217" t="s">
@@ -45538,7 +45622,7 @@
       <c r="E1246" t="s">
         <v>4569</v>
       </c>
-      <c r="F1246" s="8" t="s">
+      <c r="F1246" t="s">
         <v>4588</v>
       </c>
       <c r="G1246" s="1" t="str">
@@ -45563,7 +45647,7 @@
       <c r="E1247" t="s">
         <v>4572</v>
       </c>
-      <c r="F1247" s="8" t="s">
+      <c r="F1247" t="s">
         <v>4589</v>
       </c>
       <c r="G1247" s="1" t="str">
@@ -45588,7 +45672,7 @@
       <c r="E1248" t="s">
         <v>4575</v>
       </c>
-      <c r="F1248" s="8" t="s">
+      <c r="F1248" t="s">
         <v>4590</v>
       </c>
       <c r="G1248" s="1" t="str">
@@ -45613,7 +45697,7 @@
       <c r="E1249" t="s">
         <v>4581</v>
       </c>
-      <c r="F1249" s="8" t="s">
+      <c r="F1249" t="s">
         <v>4591</v>
       </c>
       <c r="G1249" s="1" t="str">
@@ -45638,7 +45722,7 @@
       <c r="E1250" t="s">
         <v>4580</v>
       </c>
-      <c r="F1250" s="8" t="s">
+      <c r="F1250" t="s">
         <v>4592</v>
       </c>
       <c r="G1250" s="1" t="str">
@@ -45663,7 +45747,7 @@
       <c r="E1251" t="s">
         <v>4584</v>
       </c>
-      <c r="F1251" s="8" t="s">
+      <c r="F1251" t="s">
         <v>4593</v>
       </c>
       <c r="G1251" s="1" t="str">
@@ -45688,7 +45772,7 @@
       <c r="E1252" t="s">
         <v>4587</v>
       </c>
-      <c r="F1252" s="8" t="s">
+      <c r="F1252" t="s">
         <v>4594</v>
       </c>
       <c r="G1252" s="1" t="str">
@@ -45697,38 +45781,178 @@
       </c>
     </row>
     <row r="1253" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1253" s="7" t="s">
-        <v>4315</v>
+      <c r="A1253">
+        <f t="shared" si="40"/>
+        <v>1252</v>
+      </c>
+      <c r="B1253" t="s">
+        <v>4595</v>
+      </c>
+      <c r="C1253" t="s">
+        <v>4596</v>
+      </c>
+      <c r="D1253">
+        <v>2011</v>
+      </c>
+      <c r="E1253" t="s">
+        <v>4597</v>
+      </c>
+      <c r="F1253" s="8" t="s">
+        <v>4616</v>
+      </c>
+      <c r="G1253" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/minerals.html#MakepeaceDetal2011</v>
       </c>
     </row>
     <row r="1254" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1254" s="7" t="s">
-        <v>4315</v>
+      <c r="A1254">
+        <f t="shared" si="40"/>
+        <v>1253</v>
+      </c>
+      <c r="B1254" t="s">
+        <v>4598</v>
+      </c>
+      <c r="C1254" t="s">
+        <v>4599</v>
+      </c>
+      <c r="D1254">
+        <v>1981</v>
+      </c>
+      <c r="E1254" t="s">
+        <v>4600</v>
+      </c>
+      <c r="F1254" s="8" t="s">
+        <v>4617</v>
+      </c>
+      <c r="G1254" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#RenzO1981</v>
       </c>
     </row>
     <row r="1255" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1255" s="7" t="s">
-        <v>4315</v>
+      <c r="A1255">
+        <f t="shared" si="40"/>
+        <v>1254</v>
+      </c>
+      <c r="B1255" t="s">
+        <v>4601</v>
+      </c>
+      <c r="C1255" t="s">
+        <v>4602</v>
+      </c>
+      <c r="D1255">
+        <v>1988</v>
+      </c>
+      <c r="E1255" t="s">
+        <v>4603</v>
+      </c>
+      <c r="F1255" s="8" t="s">
+        <v>4619</v>
+      </c>
+      <c r="G1255" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/ecology.html#ZimmermannW1988</v>
       </c>
     </row>
     <row r="1256" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1256" s="7" t="s">
-        <v>4315</v>
+      <c r="A1256">
+        <f t="shared" si="40"/>
+        <v>1255</v>
+      </c>
+      <c r="B1256" t="s">
+        <v>4604</v>
+      </c>
+      <c r="C1256" t="s">
+        <v>4605</v>
+      </c>
+      <c r="D1256">
+        <v>2025</v>
+      </c>
+      <c r="E1256" t="s">
+        <v>4606</v>
+      </c>
+      <c r="F1256" s="8" t="s">
+        <v>4618</v>
+      </c>
+      <c r="G1256" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/topics.html#CasasJE2025g</v>
       </c>
     </row>
     <row r="1257" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1257" s="7" t="s">
-        <v>4315</v>
+      <c r="A1257">
+        <f t="shared" si="40"/>
+        <v>1256</v>
+      </c>
+      <c r="B1257" t="s">
+        <v>4607</v>
+      </c>
+      <c r="C1257" t="s">
+        <v>4608</v>
+      </c>
+      <c r="D1257">
+        <v>1983</v>
+      </c>
+      <c r="E1257" t="s">
+        <v>4609</v>
+      </c>
+      <c r="F1257" s="8" t="s">
+        <v>4620</v>
+      </c>
+      <c r="G1257" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/geochemistry.html#JordanN1983</v>
       </c>
     </row>
     <row r="1258" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1258" s="7" t="s">
-        <v>4315</v>
+      <c r="A1258">
+        <f t="shared" si="40"/>
+        <v>1257</v>
+      </c>
+      <c r="B1258" t="s">
+        <v>4610</v>
+      </c>
+      <c r="C1258" t="s">
+        <v>4611</v>
+      </c>
+      <c r="D1258">
+        <v>1988</v>
+      </c>
+      <c r="E1258" t="s">
+        <v>4612</v>
+      </c>
+      <c r="F1258" s="8" t="s">
+        <v>4621</v>
+      </c>
+      <c r="G1258" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/structural.html#SubietaTetal1988</v>
       </c>
     </row>
     <row r="1259" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1259" s="7" t="s">
-        <v>4315</v>
+      <c r="A1259">
+        <f t="shared" si="40"/>
+        <v>1258</v>
+      </c>
+      <c r="B1259" t="s">
+        <v>4613</v>
+      </c>
+      <c r="C1259" t="s">
+        <v>4614</v>
+      </c>
+      <c r="D1259">
+        <v>1985</v>
+      </c>
+      <c r="E1259" t="s">
+        <v>4615</v>
+      </c>
+      <c r="F1259" s="8" t="s">
+        <v>4622</v>
+      </c>
+      <c r="G1259" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/excursions.html#ChevalierIetal1985</v>
       </c>
     </row>
     <row r="1260" spans="1:7" x14ac:dyDescent="0.3">
@@ -45771,8 +45995,148 @@
         <v>4315</v>
       </c>
     </row>
+    <row r="1268" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1268" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1269" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1269" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1270" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1270" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1271" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1271" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1272" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1272" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1273" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1273" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1274" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1274" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1275" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1275" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1276" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1276" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1277" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1277" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1278" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1278" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1279" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1279" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1280" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1280" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1281" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1281" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1282" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1282" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1283" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1283" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1284" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1284" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1285" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1285" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1286" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1286" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1287" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1287" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1288" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1288" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1289" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1289" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1290" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1290" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1291" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1291" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1292" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1292" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1293" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1293" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1294" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1294" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1295" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1295" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G1171" xr:uid="{6B496A77-4B74-49B4-B08F-A7274E320005}"/>
+  <autoFilter ref="A1:G1267" xr:uid="{6B496A77-4B74-49B4-B08F-A7274E320005}"/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/NotasGeologiaPublicationList_Updated.xlsx
+++ b/NotasGeologiaPublicationList_Updated.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\mariantoc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{442C7328-321C-4984-AD76-800E2FAAC76D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1282FB6E-2ACD-4F48-BE59-A1250F6AC9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14141,9 +14141,6 @@
     <t>Carta Ecológica de Lagoven S. A., Número 42, Mayo – Junio, 1988</t>
   </si>
   <si>
-    <t>Herodoto: Historiador, etnógrafo, geografo y ¿geólogo?</t>
-  </si>
-  <si>
     <t>Jhonny Edgar Casas</t>
   </si>
   <si>
@@ -14196,6 +14193,9 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/excursions.html#ChevalierIetal1985</t>
+  </si>
+  <si>
+    <t>Heródoto: Historiador, etnógrafo, geografo y ¿geólogo?</t>
   </si>
 </sst>
 </file>
@@ -14275,7 +14275,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
@@ -14288,7 +14288,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -45797,8 +45796,8 @@
       <c r="E1253" t="s">
         <v>4597</v>
       </c>
-      <c r="F1253" s="8" t="s">
-        <v>4616</v>
+      <c r="F1253" t="s">
+        <v>4615</v>
       </c>
       <c r="G1253" s="1" t="str">
         <f t="shared" si="39"/>
@@ -45822,8 +45821,8 @@
       <c r="E1254" t="s">
         <v>4600</v>
       </c>
-      <c r="F1254" s="8" t="s">
-        <v>4617</v>
+      <c r="F1254" t="s">
+        <v>4616</v>
       </c>
       <c r="G1254" s="1" t="str">
         <f t="shared" si="39"/>
@@ -45847,8 +45846,8 @@
       <c r="E1255" t="s">
         <v>4603</v>
       </c>
-      <c r="F1255" s="8" t="s">
-        <v>4619</v>
+      <c r="F1255" t="s">
+        <v>4618</v>
       </c>
       <c r="G1255" s="1" t="str">
         <f t="shared" si="39"/>
@@ -45861,19 +45860,19 @@
         <v>1255</v>
       </c>
       <c r="B1256" t="s">
+        <v>4622</v>
+      </c>
+      <c r="C1256" t="s">
         <v>4604</v>
-      </c>
-      <c r="C1256" t="s">
-        <v>4605</v>
       </c>
       <c r="D1256">
         <v>2025</v>
       </c>
       <c r="E1256" t="s">
-        <v>4606</v>
-      </c>
-      <c r="F1256" s="8" t="s">
-        <v>4618</v>
+        <v>4605</v>
+      </c>
+      <c r="F1256" t="s">
+        <v>4617</v>
       </c>
       <c r="G1256" s="1" t="str">
         <f t="shared" si="39"/>
@@ -45886,19 +45885,19 @@
         <v>1256</v>
       </c>
       <c r="B1257" t="s">
+        <v>4606</v>
+      </c>
+      <c r="C1257" t="s">
         <v>4607</v>
-      </c>
-      <c r="C1257" t="s">
-        <v>4608</v>
       </c>
       <c r="D1257">
         <v>1983</v>
       </c>
       <c r="E1257" t="s">
-        <v>4609</v>
-      </c>
-      <c r="F1257" s="8" t="s">
-        <v>4620</v>
+        <v>4608</v>
+      </c>
+      <c r="F1257" t="s">
+        <v>4619</v>
       </c>
       <c r="G1257" s="1" t="str">
         <f t="shared" si="39"/>
@@ -45911,19 +45910,19 @@
         <v>1257</v>
       </c>
       <c r="B1258" t="s">
+        <v>4609</v>
+      </c>
+      <c r="C1258" t="s">
         <v>4610</v>
-      </c>
-      <c r="C1258" t="s">
-        <v>4611</v>
       </c>
       <c r="D1258">
         <v>1988</v>
       </c>
       <c r="E1258" t="s">
-        <v>4612</v>
-      </c>
-      <c r="F1258" s="8" t="s">
-        <v>4621</v>
+        <v>4611</v>
+      </c>
+      <c r="F1258" t="s">
+        <v>4620</v>
       </c>
       <c r="G1258" s="1" t="str">
         <f t="shared" si="39"/>
@@ -45936,19 +45935,19 @@
         <v>1258</v>
       </c>
       <c r="B1259" t="s">
+        <v>4612</v>
+      </c>
+      <c r="C1259" t="s">
         <v>4613</v>
-      </c>
-      <c r="C1259" t="s">
-        <v>4614</v>
       </c>
       <c r="D1259">
         <v>1985</v>
       </c>
       <c r="E1259" t="s">
-        <v>4615</v>
-      </c>
-      <c r="F1259" s="8" t="s">
-        <v>4622</v>
+        <v>4614</v>
+      </c>
+      <c r="F1259" t="s">
+        <v>4621</v>
       </c>
       <c r="G1259" s="1" t="str">
         <f t="shared" si="39"/>

--- a/NotasGeologiaPublicationList_Updated.xlsx
+++ b/NotasGeologiaPublicationList_Updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\mariantoc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1282FB6E-2ACD-4F48-BE59-A1250F6AC9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C93F2C2-9BDF-4686-AA26-DDB64A6A5CEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -14195,7 +14195,7 @@
     <t>https://mariantoc.github.io/excursions.html#ChevalierIetal1985</t>
   </si>
   <si>
-    <t>Heródoto: Historiador, etnógrafo, geografo y ¿geólogo?</t>
+    <t>Heródoto: Historiador, etnógrafo, geógrafo y ¿geólogo?</t>
   </si>
 </sst>
 </file>

--- a/NotasGeologiaPublicationList_Updated.xlsx
+++ b/NotasGeologiaPublicationList_Updated.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\mariantoc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C93F2C2-9BDF-4686-AA26-DDB64A6A5CEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EDD14B9-EA4C-47F0-8480-F441EA58CD7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5040" uniqueCount="4623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5060" uniqueCount="4647">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -14196,6 +14196,78 @@
   </si>
   <si>
     <t>Heródoto: Historiador, etnógrafo, geógrafo y ¿geólogo?</t>
+  </si>
+  <si>
+    <t>Acta Final de la Primera Convención Venezolana de Geólogos, 17 al 20 de Septiembre de 1963.</t>
+  </si>
+  <si>
+    <t>GEOS, Número 10, pp. 79 – 82, Marzo 1964</t>
+  </si>
+  <si>
+    <t>The Guayana Highlands. Diamondiferous alluvial of the State of Bolivar, Venezuela.</t>
+  </si>
+  <si>
+    <t>The Minig Magazine, January 1946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nehil Duque. Un baluarte de Upata, estado Bolívar, Venezuela. </t>
+  </si>
+  <si>
+    <t>MAYA. Revista de Geociencias, Suplemento Mayo 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formaciones Mirador y Carbonera: Edad y relaciones estratigráficas en el Estado Táchira. </t>
+  </si>
+  <si>
+    <t>Omar Colmenares y Lizaveta Terán</t>
+  </si>
+  <si>
+    <t>Diagénesis y dolomitización en el Grupo Cogollo Inferior (Aptiense – Albiense). Un enfoque geomicrobiológico.</t>
+  </si>
+  <si>
+    <t>Daniel A. Petrash</t>
+  </si>
+  <si>
+    <t>Boletín de la Sociedad Venezolana de Geólogos, Volúmen 27, Número1, pp. 25 – 37, 2002</t>
+  </si>
+  <si>
+    <t>Intevep S.A., Departamento de Ciencias de La Tierra, 1989</t>
+  </si>
+  <si>
+    <t>Tres Parques Nacionales, tres joyas arqueológicas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magdalena de Antczak y Andrzej Antczak </t>
+  </si>
+  <si>
+    <t>Carta Ecológica de Lagoven S,A., Número 36, Mayo – Junio, 1987</t>
+  </si>
+  <si>
+    <t>El sector de las rocas y minerales industriales en Venezuela durante el año 2001.</t>
+  </si>
+  <si>
+    <t>Boletín de la Sociedad Venezolana de Geólogos, Volumen 27, Número1, pp. 67 – 68, 2002</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#Acta1963</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/minerals.html#DaveyJC1946</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#CastroM2026b</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#ColmenaresOTeranL1989</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#PetrashDA2002</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/ecology.html#AntczackMAntczackJ1987</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/minerals.html#RodriguezSE2002</t>
   </si>
 </sst>
 </file>
@@ -14275,7 +14347,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
@@ -14288,6 +14360,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -44881,13 +44954,13 @@
         <v>4472</v>
       </c>
       <c r="G1216" s="1" t="str">
-        <f t="shared" ref="G1216:G1259" si="39">HYPERLINK(F1216)</f>
+        <f t="shared" ref="G1216:G1266" si="39">HYPERLINK(F1216)</f>
         <v>https://mariantoc.github.io/minerals.html#DomenechCetal2022</v>
       </c>
     </row>
     <row r="1217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1217">
-        <f t="shared" ref="A1217:A1259" si="40">A1216+1</f>
+        <f t="shared" ref="A1217:A1266" si="40">A1216+1</f>
         <v>1216</v>
       </c>
       <c r="B1217" t="s">
@@ -45955,106 +46028,243 @@
       </c>
     </row>
     <row r="1260" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1260" s="7" t="s">
-        <v>4315</v>
+      <c r="A1260">
+        <f t="shared" si="40"/>
+        <v>1259</v>
+      </c>
+      <c r="B1260" t="s">
+        <v>4623</v>
+      </c>
+      <c r="D1260">
+        <v>1964</v>
+      </c>
+      <c r="E1260" t="s">
+        <v>4624</v>
+      </c>
+      <c r="F1260" s="8" t="s">
+        <v>4640</v>
+      </c>
+      <c r="G1260" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/biography.html#Acta1963</v>
       </c>
     </row>
     <row r="1261" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1261" s="7" t="s">
-        <v>4315</v>
+      <c r="A1261">
+        <f t="shared" si="40"/>
+        <v>1260</v>
+      </c>
+      <c r="B1261" t="s">
+        <v>4625</v>
+      </c>
+      <c r="C1261" t="s">
+        <v>4571</v>
+      </c>
+      <c r="D1261">
+        <v>1946</v>
+      </c>
+      <c r="E1261" t="s">
+        <v>4626</v>
+      </c>
+      <c r="F1261" s="8" t="s">
+        <v>4641</v>
+      </c>
+      <c r="G1261" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/minerals.html#DaveyJC1946</v>
       </c>
     </row>
     <row r="1262" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1262" s="7" t="s">
-        <v>4315</v>
+      <c r="A1262">
+        <f t="shared" si="40"/>
+        <v>1261</v>
+      </c>
+      <c r="B1262" t="s">
+        <v>4627</v>
+      </c>
+      <c r="C1262" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1262">
+        <v>2026</v>
+      </c>
+      <c r="E1262" t="s">
+        <v>4628</v>
+      </c>
+      <c r="F1262" s="8" t="s">
+        <v>4642</v>
+      </c>
+      <c r="G1262" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/biography.html#CastroM2026b</v>
       </c>
     </row>
     <row r="1263" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1263" s="7" t="s">
-        <v>4315</v>
+      <c r="A1263">
+        <f t="shared" si="40"/>
+        <v>1262</v>
+      </c>
+      <c r="B1263" t="s">
+        <v>4629</v>
+      </c>
+      <c r="C1263" t="s">
+        <v>4630</v>
+      </c>
+      <c r="D1263">
+        <v>1989</v>
+      </c>
+      <c r="E1263" t="s">
+        <v>4634</v>
+      </c>
+      <c r="F1263" s="8" t="s">
+        <v>4643</v>
+      </c>
+      <c r="G1263" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#ColmenaresOTeranL1989</v>
       </c>
     </row>
     <row r="1264" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1264" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1265" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1265" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1266" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1266" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1267" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="A1264">
+        <f t="shared" si="40"/>
+        <v>1263</v>
+      </c>
+      <c r="B1264" t="s">
+        <v>4631</v>
+      </c>
+      <c r="C1264" t="s">
+        <v>4632</v>
+      </c>
+      <c r="D1264">
+        <v>2002</v>
+      </c>
+      <c r="E1264" t="s">
+        <v>4633</v>
+      </c>
+      <c r="F1264" s="8" t="s">
+        <v>4644</v>
+      </c>
+      <c r="G1264" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#PetrashDA2002</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1265">
+        <f t="shared" si="40"/>
+        <v>1264</v>
+      </c>
+      <c r="B1265" t="s">
+        <v>4635</v>
+      </c>
+      <c r="C1265" t="s">
+        <v>4636</v>
+      </c>
+      <c r="D1265">
+        <v>1987</v>
+      </c>
+      <c r="E1265" t="s">
+        <v>4637</v>
+      </c>
+      <c r="F1265" s="8" t="s">
+        <v>4645</v>
+      </c>
+      <c r="G1265" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/ecology.html#AntczackMAntczackJ1987</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1266">
+        <f t="shared" si="40"/>
+        <v>1265</v>
+      </c>
+      <c r="B1266" t="s">
+        <v>4638</v>
+      </c>
+      <c r="C1266" t="s">
+        <v>83</v>
+      </c>
+      <c r="D1266">
+        <v>2002</v>
+      </c>
+      <c r="E1266" t="s">
+        <v>4639</v>
+      </c>
+      <c r="F1266" s="8" t="s">
+        <v>4646</v>
+      </c>
+      <c r="G1266" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/minerals.html#RodriguezSE2002</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1267" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1268" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1268" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1268" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1269" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1269" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1269" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1270" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1270" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1270" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1271" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1271" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1271" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1272" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1272" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1272" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1273" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1273" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1273" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1274" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1274" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1274" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1275" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1275" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1275" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1276" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1276" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1276" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1277" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1277" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1277" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1278" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1278" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1278" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1279" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1279" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1279" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1280" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1280" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1280" s="7" t="s">
         <v>4315</v>
       </c>

--- a/NotasGeologiaPublicationList_Updated.xlsx
+++ b/NotasGeologiaPublicationList_Updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\mariantoc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EDD14B9-EA4C-47F0-8480-F441EA58CD7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7D97058-6312-4AA4-8EB6-86D91E9B9B3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5060" uniqueCount="4647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5081" uniqueCount="4675">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -14268,6 +14268,90 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/minerals.html#RodriguezSE2002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jesús S. Porras y Genaro Stabilito </t>
+  </si>
+  <si>
+    <t>MAYA. Revista de Geociencias, Suplemento Especial, Mayo 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Piedra del Elefante: centinela del Caruachi, Guayana Venezolana. </t>
+  </si>
+  <si>
+    <t>Paleoenvironmental changes in an Aptian restricted marine basin: the Machiques Formation of western Venezuela.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Julio Vicente Pérez Infante y Paul Farrimond </t>
+  </si>
+  <si>
+    <t>Publicado en: Ǿygard, K. (ed) 1993. Organic geochemistry poster from the 16th International Meeting of Organic Geochemistry, Stavanger, Norway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mesozoic – Cenozoic tectonic and stratigraphic development of the eastern Caribbean and northern South America: Implications for eastern Venezuela and Trinidad. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">James L. Pindell </t>
+  </si>
+  <si>
+    <t>Darmouth College, Trinidad – Venezuela Project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estratigrafía del Cretáceo – Paleoceno – Eoceno de la Serranía del Interior, oriente de Venezuela. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hugo Rosales </t>
+  </si>
+  <si>
+    <t>III Congreso Geológico Venezolano, Memorias, 22 de Noviembre de 1959</t>
+  </si>
+  <si>
+    <t>Triásico.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frances Charlton de Rivero </t>
+  </si>
+  <si>
+    <t>Apuntes de las clases de Geología Histórica de la profesora Frances Charlton de Rivero en la ilustre Universidad Central de Venezuela, Escuela de Geología 1958</t>
+  </si>
+  <si>
+    <t>The Guayana Highlands. Gold deposits of the State Bolivar, Venezuela.</t>
+  </si>
+  <si>
+    <t>John C. Davey</t>
+  </si>
+  <si>
+    <t>The Mining Magazine, November 1945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo Perla, Golfo de Venezuela. Visión técnica y regulatoria para una nueva frontera energética. </t>
+  </si>
+  <si>
+    <t>José Reinaldo Sánchez Mistage</t>
+  </si>
+  <si>
+    <t>MAYA. Revista de Geociencias, Mayo 2026</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#PorrasJSStabilitoG2026</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/geochemistry.html#PerezJVFarrimondP1993</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/structural.html#PindellJL1992</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#RosalesH1959</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#CharltonF1958</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/minerals.html#DaveyJC1945</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/fields.html#SanchezJR2026</t>
   </si>
 </sst>
 </file>
@@ -44954,13 +45038,13 @@
         <v>4472</v>
       </c>
       <c r="G1216" s="1" t="str">
-        <f t="shared" ref="G1216:G1266" si="39">HYPERLINK(F1216)</f>
+        <f t="shared" ref="G1216:G1273" si="39">HYPERLINK(F1216)</f>
         <v>https://mariantoc.github.io/minerals.html#DomenechCetal2022</v>
       </c>
     </row>
     <row r="1217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1217">
-        <f t="shared" ref="A1217:A1266" si="40">A1216+1</f>
+        <f t="shared" ref="A1217:A1273" si="40">A1216+1</f>
         <v>1216</v>
       </c>
       <c r="B1217" t="s">
@@ -46041,7 +46125,7 @@
       <c r="E1260" t="s">
         <v>4624</v>
       </c>
-      <c r="F1260" s="8" t="s">
+      <c r="F1260" t="s">
         <v>4640</v>
       </c>
       <c r="G1260" s="1" t="str">
@@ -46066,7 +46150,7 @@
       <c r="E1261" t="s">
         <v>4626</v>
       </c>
-      <c r="F1261" s="8" t="s">
+      <c r="F1261" t="s">
         <v>4641</v>
       </c>
       <c r="G1261" s="1" t="str">
@@ -46091,7 +46175,7 @@
       <c r="E1262" t="s">
         <v>4628</v>
       </c>
-      <c r="F1262" s="8" t="s">
+      <c r="F1262" t="s">
         <v>4642</v>
       </c>
       <c r="G1262" s="1" t="str">
@@ -46116,7 +46200,7 @@
       <c r="E1263" t="s">
         <v>4634</v>
       </c>
-      <c r="F1263" s="8" t="s">
+      <c r="F1263" t="s">
         <v>4643</v>
       </c>
       <c r="G1263" s="1" t="str">
@@ -46141,7 +46225,7 @@
       <c r="E1264" t="s">
         <v>4633</v>
       </c>
-      <c r="F1264" s="8" t="s">
+      <c r="F1264" t="s">
         <v>4644</v>
       </c>
       <c r="G1264" s="1" t="str">
@@ -46166,7 +46250,7 @@
       <c r="E1265" t="s">
         <v>4637</v>
       </c>
-      <c r="F1265" s="8" t="s">
+      <c r="F1265" t="s">
         <v>4645</v>
       </c>
       <c r="G1265" s="1" t="str">
@@ -46191,7 +46275,7 @@
       <c r="E1266" t="s">
         <v>4639</v>
       </c>
-      <c r="F1266" s="8" t="s">
+      <c r="F1266" t="s">
         <v>4646</v>
       </c>
       <c r="G1266" s="1" t="str">
@@ -46200,38 +46284,178 @@
       </c>
     </row>
     <row r="1267" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1267" s="7" t="s">
-        <v>4315</v>
+      <c r="A1267">
+        <f t="shared" si="40"/>
+        <v>1266</v>
+      </c>
+      <c r="B1267" t="s">
+        <v>4649</v>
+      </c>
+      <c r="C1267" t="s">
+        <v>4647</v>
+      </c>
+      <c r="D1267">
+        <v>2026</v>
+      </c>
+      <c r="E1267" t="s">
+        <v>4648</v>
+      </c>
+      <c r="F1267" s="8" t="s">
+        <v>4668</v>
+      </c>
+      <c r="G1267" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/biography.html#PorrasJSStabilitoG2026</v>
       </c>
     </row>
     <row r="1268" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1268" s="7" t="s">
-        <v>4315</v>
+      <c r="A1268">
+        <f t="shared" si="40"/>
+        <v>1267</v>
+      </c>
+      <c r="B1268" t="s">
+        <v>4650</v>
+      </c>
+      <c r="C1268" t="s">
+        <v>4651</v>
+      </c>
+      <c r="D1268">
+        <v>1993</v>
+      </c>
+      <c r="E1268" t="s">
+        <v>4652</v>
+      </c>
+      <c r="F1268" s="8" t="s">
+        <v>4669</v>
+      </c>
+      <c r="G1268" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/geochemistry.html#PerezJVFarrimondP1993</v>
       </c>
     </row>
     <row r="1269" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1269" s="7" t="s">
-        <v>4315</v>
+      <c r="A1269">
+        <f t="shared" si="40"/>
+        <v>1268</v>
+      </c>
+      <c r="B1269" t="s">
+        <v>4653</v>
+      </c>
+      <c r="C1269" t="s">
+        <v>4654</v>
+      </c>
+      <c r="D1269">
+        <v>1992</v>
+      </c>
+      <c r="E1269" t="s">
+        <v>4655</v>
+      </c>
+      <c r="F1269" s="8" t="s">
+        <v>4670</v>
+      </c>
+      <c r="G1269" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/structural.html#PindellJL1992</v>
       </c>
     </row>
     <row r="1270" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1270" s="7" t="s">
-        <v>4315</v>
+      <c r="A1270">
+        <f t="shared" si="40"/>
+        <v>1269</v>
+      </c>
+      <c r="B1270" t="s">
+        <v>4656</v>
+      </c>
+      <c r="C1270" t="s">
+        <v>4657</v>
+      </c>
+      <c r="D1270">
+        <v>1959</v>
+      </c>
+      <c r="E1270" t="s">
+        <v>4658</v>
+      </c>
+      <c r="F1270" s="8" t="s">
+        <v>4671</v>
+      </c>
+      <c r="G1270" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#RosalesH1959</v>
       </c>
     </row>
     <row r="1271" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1271" s="7" t="s">
-        <v>4315</v>
+      <c r="A1271">
+        <f t="shared" si="40"/>
+        <v>1270</v>
+      </c>
+      <c r="B1271" t="s">
+        <v>4659</v>
+      </c>
+      <c r="C1271" t="s">
+        <v>4660</v>
+      </c>
+      <c r="D1271">
+        <v>1958</v>
+      </c>
+      <c r="E1271" t="s">
+        <v>4661</v>
+      </c>
+      <c r="F1271" s="8" t="s">
+        <v>4672</v>
+      </c>
+      <c r="G1271" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#CharltonF1958</v>
       </c>
     </row>
     <row r="1272" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1272" s="7" t="s">
-        <v>4315</v>
+      <c r="A1272">
+        <f t="shared" si="40"/>
+        <v>1271</v>
+      </c>
+      <c r="B1272" t="s">
+        <v>4662</v>
+      </c>
+      <c r="C1272" t="s">
+        <v>4663</v>
+      </c>
+      <c r="D1272">
+        <v>1945</v>
+      </c>
+      <c r="E1272" t="s">
+        <v>4664</v>
+      </c>
+      <c r="F1272" s="8" t="s">
+        <v>4673</v>
+      </c>
+      <c r="G1272" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/minerals.html#DaveyJC1945</v>
       </c>
     </row>
     <row r="1273" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1273" s="7" t="s">
-        <v>4315</v>
+      <c r="A1273">
+        <f t="shared" si="40"/>
+        <v>1272</v>
+      </c>
+      <c r="B1273" t="s">
+        <v>4665</v>
+      </c>
+      <c r="C1273" t="s">
+        <v>4666</v>
+      </c>
+      <c r="D1273">
+        <v>2026</v>
+      </c>
+      <c r="E1273" t="s">
+        <v>4667</v>
+      </c>
+      <c r="F1273" s="8" t="s">
+        <v>4674</v>
+      </c>
+      <c r="G1273" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/fields.html#SanchezJR2026</v>
       </c>
     </row>
     <row r="1274" spans="1:7" x14ac:dyDescent="0.3">

--- a/NotasGeologiaPublicationList_Updated.xlsx
+++ b/NotasGeologiaPublicationList_Updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\mariantoc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7D97058-6312-4AA4-8EB6-86D91E9B9B3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0648610-D7E1-4442-A587-A2A8554EE5C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5081" uniqueCount="4675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5101" uniqueCount="4699">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -14352,6 +14352,78 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/fields.html#SanchezJR2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">José María Vargas: Precursor de las Geociencias en Venezuela. </t>
+  </si>
+  <si>
+    <t>Jesús S. Porras</t>
+  </si>
+  <si>
+    <t>Moluscos representativos de la Plataforma de Margarita, Venezuela.</t>
+  </si>
+  <si>
+    <t>Oliver Macsotay y Régulo Campos Villaroel</t>
+  </si>
+  <si>
+    <t>Editorial Rivolta, Valencia, Venezuela, Julio 2001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jurásico. </t>
+  </si>
+  <si>
+    <t>¿Es la “Brea del Buen Pastor” de Alejandro de Humbolt la misma localidad que el “Lago de Asfalto de Guanoco”?</t>
+  </si>
+  <si>
+    <t>Franco Urbani Patat; Peter Hardetert y Martín Guntau</t>
+  </si>
+  <si>
+    <t>Boletín de Historia de las Geociencias en Venezuela, Volumen 54, pp. 27 – 32, 1995</t>
+  </si>
+  <si>
+    <t>The Venezuelan El Dorado. A progressive Government Favours New Mining Enterprise.</t>
+  </si>
+  <si>
+    <t>J. C. Davey</t>
+  </si>
+  <si>
+    <t>Canadian Mining Journal, November 1943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evelyn Quintero: Un liderazgo forjado en valores. </t>
+  </si>
+  <si>
+    <t>Petrorenova. Revista de la Energía, Volumen 4, Numero 33, Mayo 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geopolítica y sostenibilidad minera: Un análisis integral sobre tierras raras y minerales críticos en el contexto venezolano actual. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noel Mariňo Pardo </t>
+  </si>
+  <si>
+    <t>Boletín de la Academia Nacional de la Ingeniería y el Hábitat, Número 70, Enero – Marzo, 2026</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#PorrasJS2026</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#MacsotayOCamposR2001</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#CharltonF1958a</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/fields.html#UrbaniFetal1995</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/minerals.html#DaveyJC1943</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#Petrorenova2026</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/minerals.html#MarinoN2026</t>
   </si>
 </sst>
 </file>
@@ -45038,13 +45110,13 @@
         <v>4472</v>
       </c>
       <c r="G1216" s="1" t="str">
-        <f t="shared" ref="G1216:G1273" si="39">HYPERLINK(F1216)</f>
+        <f t="shared" ref="G1216:G1279" si="39">HYPERLINK(F1216)</f>
         <v>https://mariantoc.github.io/minerals.html#DomenechCetal2022</v>
       </c>
     </row>
     <row r="1217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1217">
-        <f t="shared" ref="A1217:A1273" si="40">A1216+1</f>
+        <f t="shared" ref="A1217:A1280" si="40">A1216+1</f>
         <v>1216</v>
       </c>
       <c r="B1217" t="s">
@@ -46300,7 +46372,7 @@
       <c r="E1267" t="s">
         <v>4648</v>
       </c>
-      <c r="F1267" s="8" t="s">
+      <c r="F1267" t="s">
         <v>4668</v>
       </c>
       <c r="G1267" s="1" t="str">
@@ -46325,7 +46397,7 @@
       <c r="E1268" t="s">
         <v>4652</v>
       </c>
-      <c r="F1268" s="8" t="s">
+      <c r="F1268" t="s">
         <v>4669</v>
       </c>
       <c r="G1268" s="1" t="str">
@@ -46350,7 +46422,7 @@
       <c r="E1269" t="s">
         <v>4655</v>
       </c>
-      <c r="F1269" s="8" t="s">
+      <c r="F1269" t="s">
         <v>4670</v>
       </c>
       <c r="G1269" s="1" t="str">
@@ -46375,7 +46447,7 @@
       <c r="E1270" t="s">
         <v>4658</v>
       </c>
-      <c r="F1270" s="8" t="s">
+      <c r="F1270" t="s">
         <v>4671</v>
       </c>
       <c r="G1270" s="1" t="str">
@@ -46400,7 +46472,7 @@
       <c r="E1271" t="s">
         <v>4661</v>
       </c>
-      <c r="F1271" s="8" t="s">
+      <c r="F1271" t="s">
         <v>4672</v>
       </c>
       <c r="G1271" s="1" t="str">
@@ -46425,7 +46497,7 @@
       <c r="E1272" t="s">
         <v>4664</v>
       </c>
-      <c r="F1272" s="8" t="s">
+      <c r="F1272" t="s">
         <v>4673</v>
       </c>
       <c r="G1272" s="1" t="str">
@@ -46450,7 +46522,7 @@
       <c r="E1273" t="s">
         <v>4667</v>
       </c>
-      <c r="F1273" s="8" t="s">
+      <c r="F1273" t="s">
         <v>4674</v>
       </c>
       <c r="G1273" s="1" t="str">
@@ -46459,38 +46531,175 @@
       </c>
     </row>
     <row r="1274" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1274" s="7" t="s">
-        <v>4315</v>
+      <c r="A1274">
+        <f t="shared" si="40"/>
+        <v>1273</v>
+      </c>
+      <c r="B1274" t="s">
+        <v>4675</v>
+      </c>
+      <c r="C1274" t="s">
+        <v>4676</v>
+      </c>
+      <c r="D1274">
+        <v>2026</v>
+      </c>
+      <c r="E1274" t="s">
+        <v>4628</v>
+      </c>
+      <c r="F1274" s="8" t="s">
+        <v>4692</v>
+      </c>
+      <c r="G1274" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/biography.html#PorrasJS2026</v>
       </c>
     </row>
     <row r="1275" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1275" s="7" t="s">
-        <v>4315</v>
+      <c r="A1275">
+        <f t="shared" si="40"/>
+        <v>1274</v>
+      </c>
+      <c r="B1275" t="s">
+        <v>4677</v>
+      </c>
+      <c r="C1275" t="s">
+        <v>4678</v>
+      </c>
+      <c r="D1275">
+        <v>2001</v>
+      </c>
+      <c r="E1275" t="s">
+        <v>4679</v>
+      </c>
+      <c r="F1275" s="8" t="s">
+        <v>4693</v>
+      </c>
+      <c r="G1275" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#MacsotayOCamposR2001</v>
       </c>
     </row>
     <row r="1276" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1276" s="7" t="s">
-        <v>4315</v>
+      <c r="A1276">
+        <f t="shared" si="40"/>
+        <v>1275</v>
+      </c>
+      <c r="B1276" t="s">
+        <v>4680</v>
+      </c>
+      <c r="C1276" t="s">
+        <v>4660</v>
+      </c>
+      <c r="D1276">
+        <v>1958</v>
+      </c>
+      <c r="E1276" t="s">
+        <v>4661</v>
+      </c>
+      <c r="F1276" s="8" t="s">
+        <v>4694</v>
+      </c>
+      <c r="G1276" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#CharltonF1958a</v>
       </c>
     </row>
     <row r="1277" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1277" s="7" t="s">
-        <v>4315</v>
+      <c r="A1277">
+        <f t="shared" si="40"/>
+        <v>1276</v>
+      </c>
+      <c r="B1277" t="s">
+        <v>4681</v>
+      </c>
+      <c r="C1277" t="s">
+        <v>4682</v>
+      </c>
+      <c r="D1277">
+        <v>1995</v>
+      </c>
+      <c r="E1277" t="s">
+        <v>4683</v>
+      </c>
+      <c r="F1277" s="8" t="s">
+        <v>4695</v>
+      </c>
+      <c r="G1277" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/fields.html#UrbaniFetal1995</v>
       </c>
     </row>
     <row r="1278" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1278" s="7" t="s">
-        <v>4315</v>
+      <c r="A1278">
+        <f t="shared" si="40"/>
+        <v>1277</v>
+      </c>
+      <c r="B1278" t="s">
+        <v>4684</v>
+      </c>
+      <c r="C1278" t="s">
+        <v>4685</v>
+      </c>
+      <c r="D1278">
+        <v>1943</v>
+      </c>
+      <c r="E1278" t="s">
+        <v>4686</v>
+      </c>
+      <c r="F1278" s="8" t="s">
+        <v>4696</v>
+      </c>
+      <c r="G1278" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/minerals.html#DaveyJC1943</v>
       </c>
     </row>
     <row r="1279" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1279" s="7" t="s">
-        <v>4315</v>
+      <c r="A1279">
+        <f t="shared" si="40"/>
+        <v>1278</v>
+      </c>
+      <c r="B1279" t="s">
+        <v>4687</v>
+      </c>
+      <c r="D1279">
+        <v>2026</v>
+      </c>
+      <c r="E1279" t="s">
+        <v>4688</v>
+      </c>
+      <c r="F1279" s="8" t="s">
+        <v>4697</v>
+      </c>
+      <c r="G1279" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/biography.html#Petrorenova2026</v>
       </c>
     </row>
     <row r="1280" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1280" s="7" t="s">
-        <v>4315</v>
+      <c r="A1280">
+        <f t="shared" si="40"/>
+        <v>1279</v>
+      </c>
+      <c r="B1280" t="s">
+        <v>4689</v>
+      </c>
+      <c r="C1280" t="s">
+        <v>4690</v>
+      </c>
+      <c r="D1280">
+        <v>2026</v>
+      </c>
+      <c r="E1280" t="s">
+        <v>4691</v>
+      </c>
+      <c r="F1280" s="8" t="s">
+        <v>4698</v>
+      </c>
+      <c r="G1280" s="1" t="str">
+        <f t="shared" ref="G1280" si="41">HYPERLINK(F1280)</f>
+        <v>https://mariantoc.github.io/minerals.html#MarinoN2026</v>
       </c>
     </row>
     <row r="1281" spans="6:6" x14ac:dyDescent="0.3">

--- a/NotasGeologiaPublicationList_Updated.xlsx
+++ b/NotasGeologiaPublicationList_Updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\mariantoc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0648610-D7E1-4442-A587-A2A8554EE5C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A2AC314-3EC3-4E1D-9493-051314950E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5101" uniqueCount="4699">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5205" uniqueCount="4724">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -14399,9 +14399,6 @@
     <t xml:space="preserve">Geopolítica y sostenibilidad minera: Un análisis integral sobre tierras raras y minerales críticos en el contexto venezolano actual. </t>
   </si>
   <si>
-    <t xml:space="preserve">Noel Mariňo Pardo </t>
-  </si>
-  <si>
     <t>Boletín de la Academia Nacional de la Ingeniería y el Hábitat, Número 70, Enero – Marzo, 2026</t>
   </si>
   <si>
@@ -14424,6 +14421,84 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/minerals.html#MarinoN2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exploración y evaluación geológica, económica, socio – ambiental y procesamiento del mineral azavache localizado en el Río Orinoco, sectores Vuelta El Toro – El Merey, Municipio Sucre y Caicara del Orinoco – Puerto El Burro, Municipio Cedeño del Estado Bolívar. </t>
+  </si>
+  <si>
+    <t>Ayala, T.; Malavé, M.; Rodríguez, S.; Herrero, J.; Angel, R.; Paulo, G.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noel Mariño Pardo </t>
+  </si>
+  <si>
+    <t>Geominas, Volumen 34, Número 51, Abril 2010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rocas industriales de Venezuela. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">López, V. M.; Ascanio, G.; Guerrero, V. R. </t>
+  </si>
+  <si>
+    <t>Rocas Industriales de Venezuela, Fundacite Aragua. Actualizado y ampliado por José Luis Bertorelli, pp. 31 – 42, 2003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gravitational deposits in Venezuela. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">R. M. Stainforth </t>
+  </si>
+  <si>
+    <t>Boletín Informativo de la Asociación Venezolana de Geología, Minería y Petróleo, Volumen 9, Número 10, Octubre 1966</t>
+  </si>
+  <si>
+    <t>Los veinte años de la Promoción Cajigal 1945 -1965. Geólogos de la Promoción Cajigal, Escuela de Geología, Universidad Central de Venezuela, Avenida San Martín.</t>
+  </si>
+  <si>
+    <t>Revista GEOS, Número 14, Junio 1966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formaciones Cenozoicas de Paria, secciones detalladas, correlaciones, paleontología y paleoecología con descripción de nuevas especies. </t>
+  </si>
+  <si>
+    <t>Revista GEOS, Número 17, Mayo 1968</t>
+  </si>
+  <si>
+    <t>Resúmen de foraminíferos presentes en Monagas en las áreas de responsabilidad exploratoria de Lagoven S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marianto Castro Mora y Marco Odehnal </t>
+  </si>
+  <si>
+    <t>Tabla resúmen realizada para Lagoven S.A. 1987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las costas venezolanas: Asilo de avifauna migratoria </t>
+  </si>
+  <si>
+    <t>Carta Ecológica Lagoven S.A., Número 37, Julio – Agosto, 1987</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/minerals.html#Ayalaetal2010</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/minerals.html#LopezVMetal2003</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#StainforthRM1966</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#PromocionCajigal1945</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#MacsotayO1968a</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#CastroMOdehnalM1987</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/ecology.html#Costas1987</t>
   </si>
 </sst>
 </file>
@@ -14503,7 +14578,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
@@ -14516,7 +14591,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -14832,7 +14906,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B496A77-4B74-49B4-B08F-A7274E320005}">
-  <dimension ref="A1:H1295"/>
+  <dimension ref="A1:H1380"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="66.5546875" customWidth="1"/>
@@ -45110,13 +45184,13 @@
         <v>4472</v>
       </c>
       <c r="G1216" s="1" t="str">
-        <f t="shared" ref="G1216:G1279" si="39">HYPERLINK(F1216)</f>
+        <f t="shared" ref="G1216:G1280" si="39">HYPERLINK(F1216)</f>
         <v>https://mariantoc.github.io/minerals.html#DomenechCetal2022</v>
       </c>
     </row>
     <row r="1217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1217">
-        <f t="shared" ref="A1217:A1280" si="40">A1216+1</f>
+        <f t="shared" ref="A1217:A1281" si="40">A1216+1</f>
         <v>1216</v>
       </c>
       <c r="B1217" t="s">
@@ -46547,8 +46621,8 @@
       <c r="E1274" t="s">
         <v>4628</v>
       </c>
-      <c r="F1274" s="8" t="s">
-        <v>4692</v>
+      <c r="F1274" t="s">
+        <v>4691</v>
       </c>
       <c r="G1274" s="1" t="str">
         <f t="shared" si="39"/>
@@ -46572,8 +46646,8 @@
       <c r="E1275" t="s">
         <v>4679</v>
       </c>
-      <c r="F1275" s="8" t="s">
-        <v>4693</v>
+      <c r="F1275" t="s">
+        <v>4692</v>
       </c>
       <c r="G1275" s="1" t="str">
         <f t="shared" si="39"/>
@@ -46597,8 +46671,8 @@
       <c r="E1276" t="s">
         <v>4661</v>
       </c>
-      <c r="F1276" s="8" t="s">
-        <v>4694</v>
+      <c r="F1276" t="s">
+        <v>4693</v>
       </c>
       <c r="G1276" s="1" t="str">
         <f t="shared" si="39"/>
@@ -46622,8 +46696,8 @@
       <c r="E1277" t="s">
         <v>4683</v>
       </c>
-      <c r="F1277" s="8" t="s">
-        <v>4695</v>
+      <c r="F1277" t="s">
+        <v>4694</v>
       </c>
       <c r="G1277" s="1" t="str">
         <f t="shared" si="39"/>
@@ -46647,8 +46721,8 @@
       <c r="E1278" t="s">
         <v>4686</v>
       </c>
-      <c r="F1278" s="8" t="s">
-        <v>4696</v>
+      <c r="F1278" t="s">
+        <v>4695</v>
       </c>
       <c r="G1278" s="1" t="str">
         <f t="shared" si="39"/>
@@ -46669,8 +46743,8 @@
       <c r="E1279" t="s">
         <v>4688</v>
       </c>
-      <c r="F1279" s="8" t="s">
-        <v>4697</v>
+      <c r="F1279" t="s">
+        <v>4696</v>
       </c>
       <c r="G1279" s="1" t="str">
         <f t="shared" si="39"/>
@@ -46686,101 +46760,672 @@
         <v>4689</v>
       </c>
       <c r="C1280" t="s">
-        <v>4690</v>
+        <v>4700</v>
       </c>
       <c r="D1280">
         <v>2026</v>
       </c>
       <c r="E1280" t="s">
-        <v>4691</v>
-      </c>
-      <c r="F1280" s="8" t="s">
+        <v>4690</v>
+      </c>
+      <c r="F1280" t="s">
+        <v>4697</v>
+      </c>
+      <c r="G1280" s="1" t="str">
+        <f t="shared" si="39"/>
+        <v>https://mariantoc.github.io/minerals.html#MarinoN2026</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1281">
+        <f t="shared" si="40"/>
+        <v>1280</v>
+      </c>
+      <c r="B1281" t="s">
         <v>4698</v>
       </c>
-      <c r="G1280" s="1" t="str">
-        <f t="shared" ref="G1280" si="41">HYPERLINK(F1280)</f>
-        <v>https://mariantoc.github.io/minerals.html#MarinoN2026</v>
-      </c>
-    </row>
-    <row r="1281" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="C1281" t="s">
+        <v>4699</v>
+      </c>
+      <c r="D1281">
+        <v>2010</v>
+      </c>
+      <c r="E1281" t="s">
+        <v>4701</v>
+      </c>
       <c r="F1281" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1282" spans="6:6" x14ac:dyDescent="0.3">
+        <v>4717</v>
+      </c>
+      <c r="G1281" s="1" t="str">
+        <f t="shared" ref="G1281:G1290" si="41">HYPERLINK(F1281)</f>
+        <v>https://mariantoc.github.io/minerals.html#Ayalaetal2010</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1282">
+        <f t="shared" ref="A1282:A1287" si="42">A1281+1</f>
+        <v>1281</v>
+      </c>
+      <c r="B1282" t="s">
+        <v>4702</v>
+      </c>
+      <c r="C1282" t="s">
+        <v>4703</v>
+      </c>
+      <c r="D1282">
+        <v>2003</v>
+      </c>
+      <c r="E1282" t="s">
+        <v>4704</v>
+      </c>
       <c r="F1282" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1283" spans="6:6" x14ac:dyDescent="0.3">
+        <v>4718</v>
+      </c>
+      <c r="G1282" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/minerals.html#LopezVMetal2003</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1283">
+        <f t="shared" si="42"/>
+        <v>1282</v>
+      </c>
+      <c r="B1283" t="s">
+        <v>4705</v>
+      </c>
+      <c r="C1283" t="s">
+        <v>4706</v>
+      </c>
+      <c r="D1283">
+        <v>1966</v>
+      </c>
+      <c r="E1283" t="s">
+        <v>4707</v>
+      </c>
       <c r="F1283" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1284" spans="6:6" x14ac:dyDescent="0.3">
+        <v>4719</v>
+      </c>
+      <c r="G1283" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#StainforthRM1966</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1284">
+        <f t="shared" si="42"/>
+        <v>1283</v>
+      </c>
+      <c r="B1284" t="s">
+        <v>4708</v>
+      </c>
+      <c r="D1284">
+        <v>1966</v>
+      </c>
+      <c r="E1284" t="s">
+        <v>4709</v>
+      </c>
       <c r="F1284" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1285" spans="6:6" x14ac:dyDescent="0.3">
+        <v>4720</v>
+      </c>
+      <c r="G1284" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/biography.html#PromocionCajigal1945</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1285">
+        <f t="shared" si="42"/>
+        <v>1284</v>
+      </c>
+      <c r="B1285" t="s">
+        <v>4710</v>
+      </c>
+      <c r="C1285" t="s">
+        <v>2239</v>
+      </c>
+      <c r="D1285">
+        <v>1968</v>
+      </c>
+      <c r="E1285" t="s">
+        <v>4711</v>
+      </c>
       <c r="F1285" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1286" spans="6:6" x14ac:dyDescent="0.3">
+        <v>4721</v>
+      </c>
+      <c r="G1285" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#MacsotayO1968a</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1286">
+        <f t="shared" si="42"/>
+        <v>1285</v>
+      </c>
+      <c r="B1286" t="s">
+        <v>4712</v>
+      </c>
+      <c r="C1286" t="s">
+        <v>4713</v>
+      </c>
+      <c r="D1286">
+        <v>1987</v>
+      </c>
+      <c r="E1286" t="s">
+        <v>4714</v>
+      </c>
       <c r="F1286" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1287" spans="6:6" x14ac:dyDescent="0.3">
+        <v>4722</v>
+      </c>
+      <c r="G1286" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#CastroMOdehnalM1987</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1287">
+        <f t="shared" si="42"/>
+        <v>1286</v>
+      </c>
+      <c r="B1287" t="s">
+        <v>4715</v>
+      </c>
+      <c r="D1287">
+        <v>1987</v>
+      </c>
+      <c r="E1287" t="s">
+        <v>4716</v>
+      </c>
       <c r="F1287" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1288" spans="6:6" x14ac:dyDescent="0.3">
+        <v>4723</v>
+      </c>
+      <c r="G1287" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/ecology.html#Costas1987</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1288" s="7" t="s">
         <v>4315</v>
       </c>
-    </row>
-    <row r="1289" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="G1288" s="1"/>
+    </row>
+    <row r="1289" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1289" s="7" t="s">
         <v>4315</v>
       </c>
-    </row>
-    <row r="1290" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="G1289" s="1"/>
+    </row>
+    <row r="1290" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1290" s="7" t="s">
         <v>4315</v>
       </c>
-    </row>
-    <row r="1291" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="G1290" s="1"/>
+    </row>
+    <row r="1291" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1291" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1292" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1292" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1292" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1293" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1293" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1293" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1294" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1294" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1294" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1295" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1295" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1295" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F1296" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1297" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1297" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1298" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1298" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1299" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1299" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1300" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1300" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1301" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1301" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1302" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1302" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1303" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1303" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1304" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1304" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1305" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1305" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1306" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1306" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1307" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1307" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1308" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1308" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1309" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1309" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1310" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1310" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1311" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1311" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1312" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1312" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1313" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1313" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1314" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1314" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1315" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1315" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1316" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1316" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1317" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1317" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1318" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1318" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1319" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1319" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1320" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1320" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1321" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1321" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1322" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1322" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1323" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1323" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1324" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1324" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1325" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1325" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1326" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1326" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1327" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1327" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1328" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1328" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1329" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1329" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1330" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1330" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1331" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1331" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1332" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1332" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1333" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1333" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1334" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1334" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1335" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1335" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1336" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1336" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1337" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1337" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1338" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1338" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1339" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1339" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1340" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1340" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1341" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1341" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1342" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1342" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1343" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1343" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1344" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1344" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1345" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1345" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1346" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1346" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1347" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1347" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1348" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1348" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1349" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1349" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1350" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1350" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1351" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1351" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1352" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1352" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1353" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1353" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1354" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1354" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1355" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1355" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1356" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1356" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1357" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1357" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1358" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1358" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1359" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1359" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1360" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1360" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1361" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1361" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1362" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1362" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1363" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1363" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1364" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1364" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1365" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1365" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1366" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1366" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1367" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1367" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1368" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1368" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1369" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1369" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1370" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1370" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1371" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1371" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1372" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1372" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1373" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1373" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1374" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1374" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1375" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1375" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1376" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1376" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1377" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1377" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1378" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1378" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1379" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1379" s="7" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1380" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1380" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G1267" xr:uid="{6B496A77-4B74-49B4-B08F-A7274E320005}"/>
   <phoneticPr fontId="4" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="F1281" r:id="rId1" location="Ayalaetal2010" xr:uid="{961B0CD1-124D-4C97-94CB-D327D72148B1}"/>
+    <hyperlink ref="F1282" r:id="rId2" location="LopezVMetal2003" xr:uid="{2F92AD89-067E-45B9-875B-AF47DEAD04ED}"/>
+    <hyperlink ref="F1283" r:id="rId3" location="StainforthRM1966" xr:uid="{F5664ED0-3F59-4F67-8AF3-C3A0E65CAA9C}"/>
+    <hyperlink ref="F1284" r:id="rId4" location="PromocionCajigal1945" xr:uid="{5984370C-BB6E-4CA0-8630-9AECDDFDAF0D}"/>
+    <hyperlink ref="F1285" r:id="rId5" location="MacsotayO1968a" xr:uid="{3CDD1149-4EBE-48E6-A408-B04868E6C0FC}"/>
+    <hyperlink ref="F1286" r:id="rId6" location="CastroMOdehnalM1987" xr:uid="{C9F42AF9-A565-4865-8D6D-48B025112588}"/>
+    <hyperlink ref="F1287" r:id="rId7" location="Costas1987" xr:uid="{8C448E11-3A46-4D58-9B4D-2BD8B435036C}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId8"/>
 </worksheet>
 </file>
--- a/NotasGeologiaPublicationList_Updated.xlsx
+++ b/NotasGeologiaPublicationList_Updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\mariantoc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A2AC314-3EC3-4E1D-9493-051314950E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{188A8259-F956-46CC-800C-BFA75CE96641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -14423,9 +14423,6 @@
     <t>https://mariantoc.github.io/minerals.html#MarinoN2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Exploración y evaluación geológica, económica, socio – ambiental y procesamiento del mineral azavache localizado en el Río Orinoco, sectores Vuelta El Toro – El Merey, Municipio Sucre y Caicara del Orinoco – Puerto El Burro, Municipio Cedeño del Estado Bolívar. </t>
-  </si>
-  <si>
     <t>Ayala, T.; Malavé, M.; Rodríguez, S.; Herrero, J.; Angel, R.; Paulo, G.</t>
   </si>
   <si>
@@ -14499,13 +14496,39 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/ecology.html#Costas1987</t>
+  </si>
+  <si>
+    <r>
+      <t>Exploración y evaluación geológica, económica, socio – ambiental y procesamiento del mineral aza</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>b</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">ache localizado en el Río Orinoco, sectores Vuelta El Toro – El Merey, Municipio Sucre y Caicara del Orinoco – Puerto El Burro, Municipio Cedeño del Estado Bolívar. </t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -14552,6 +14575,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -46760,7 +46791,7 @@
         <v>4689</v>
       </c>
       <c r="C1280" t="s">
-        <v>4700</v>
+        <v>4699</v>
       </c>
       <c r="D1280">
         <v>2026</v>
@@ -46782,22 +46813,22 @@
         <v>1280</v>
       </c>
       <c r="B1281" t="s">
+        <v>4723</v>
+      </c>
+      <c r="C1281" t="s">
         <v>4698</v>
-      </c>
-      <c r="C1281" t="s">
-        <v>4699</v>
       </c>
       <c r="D1281">
         <v>2010</v>
       </c>
       <c r="E1281" t="s">
-        <v>4701</v>
+        <v>4700</v>
       </c>
       <c r="F1281" s="7" t="s">
-        <v>4717</v>
+        <v>4716</v>
       </c>
       <c r="G1281" s="1" t="str">
-        <f t="shared" ref="G1281:G1290" si="41">HYPERLINK(F1281)</f>
+        <f t="shared" ref="G1281:G1287" si="41">HYPERLINK(F1281)</f>
         <v>https://mariantoc.github.io/minerals.html#Ayalaetal2010</v>
       </c>
     </row>
@@ -46807,19 +46838,19 @@
         <v>1281</v>
       </c>
       <c r="B1282" t="s">
+        <v>4701</v>
+      </c>
+      <c r="C1282" t="s">
         <v>4702</v>
-      </c>
-      <c r="C1282" t="s">
-        <v>4703</v>
       </c>
       <c r="D1282">
         <v>2003</v>
       </c>
       <c r="E1282" t="s">
-        <v>4704</v>
+        <v>4703</v>
       </c>
       <c r="F1282" s="7" t="s">
-        <v>4718</v>
+        <v>4717</v>
       </c>
       <c r="G1282" s="1" t="str">
         <f t="shared" si="41"/>
@@ -46832,19 +46863,19 @@
         <v>1282</v>
       </c>
       <c r="B1283" t="s">
+        <v>4704</v>
+      </c>
+      <c r="C1283" t="s">
         <v>4705</v>
-      </c>
-      <c r="C1283" t="s">
-        <v>4706</v>
       </c>
       <c r="D1283">
         <v>1966</v>
       </c>
       <c r="E1283" t="s">
-        <v>4707</v>
+        <v>4706</v>
       </c>
       <c r="F1283" s="7" t="s">
-        <v>4719</v>
+        <v>4718</v>
       </c>
       <c r="G1283" s="1" t="str">
         <f t="shared" si="41"/>
@@ -46857,16 +46888,16 @@
         <v>1283</v>
       </c>
       <c r="B1284" t="s">
-        <v>4708</v>
+        <v>4707</v>
       </c>
       <c r="D1284">
         <v>1966</v>
       </c>
       <c r="E1284" t="s">
-        <v>4709</v>
+        <v>4708</v>
       </c>
       <c r="F1284" s="7" t="s">
-        <v>4720</v>
+        <v>4719</v>
       </c>
       <c r="G1284" s="1" t="str">
         <f t="shared" si="41"/>
@@ -46879,7 +46910,7 @@
         <v>1284</v>
       </c>
       <c r="B1285" t="s">
-        <v>4710</v>
+        <v>4709</v>
       </c>
       <c r="C1285" t="s">
         <v>2239</v>
@@ -46888,10 +46919,10 @@
         <v>1968</v>
       </c>
       <c r="E1285" t="s">
-        <v>4711</v>
+        <v>4710</v>
       </c>
       <c r="F1285" s="7" t="s">
-        <v>4721</v>
+        <v>4720</v>
       </c>
       <c r="G1285" s="1" t="str">
         <f t="shared" si="41"/>
@@ -46904,19 +46935,19 @@
         <v>1285</v>
       </c>
       <c r="B1286" t="s">
+        <v>4711</v>
+      </c>
+      <c r="C1286" t="s">
         <v>4712</v>
-      </c>
-      <c r="C1286" t="s">
-        <v>4713</v>
       </c>
       <c r="D1286">
         <v>1987</v>
       </c>
       <c r="E1286" t="s">
-        <v>4714</v>
+        <v>4713</v>
       </c>
       <c r="F1286" s="7" t="s">
-        <v>4722</v>
+        <v>4721</v>
       </c>
       <c r="G1286" s="1" t="str">
         <f t="shared" si="41"/>
@@ -46929,16 +46960,16 @@
         <v>1286</v>
       </c>
       <c r="B1287" t="s">
-        <v>4715</v>
+        <v>4714</v>
       </c>
       <c r="D1287">
         <v>1987</v>
       </c>
       <c r="E1287" t="s">
-        <v>4716</v>
+        <v>4715</v>
       </c>
       <c r="F1287" s="7" t="s">
-        <v>4723</v>
+        <v>4722</v>
       </c>
       <c r="G1287" s="1" t="str">
         <f t="shared" si="41"/>
